--- a/04_DESIGN_TABLES/DesignTable_6410_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6410_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK31"/>
+  <dimension ref="A1:AK35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,17 +734,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6410-04-04-O</t>
+          <t>6410-04-02-O</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1.1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.36084</v>
+        <v>0.32447</v>
       </c>
       <c r="D3" t="n">
-        <v>0.625</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="E3" t="n">
         <v>0.21875</v>
@@ -777,55 +777,55 @@
         <v>0.05</v>
       </c>
       <c r="O3" t="n">
-        <v>0.245</v>
+        <v>0.18</v>
       </c>
       <c r="P3" t="n">
         <v>12</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2233</v>
+        <v>0.1624</v>
       </c>
       <c r="R3" t="n">
-        <v>0.19</v>
+        <v>0.135</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4116</v>
+        <v>0.3578</v>
       </c>
       <c r="T3" t="n">
         <v>60</v>
       </c>
       <c r="U3" t="n">
-        <v>0.38</v>
+        <v>0.27</v>
       </c>
       <c r="V3" t="n">
-        <v>0.547</v>
+        <v>0.468</v>
       </c>
       <c r="W3" t="n">
-        <v>0.05</v>
+        <v>0.04167</v>
       </c>
       <c r="X3" t="n">
-        <v>0.19</v>
+        <v>0.135</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.21706</v>
+        <v>0.15755</v>
       </c>
       <c r="Z3" t="n">
         <v>1.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.17</v>
+        <v>0.172</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.553</v>
+        <v>0.632</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>6410-04-04-O</t>
+          <t>6410-04-02-O</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 7/16-20 (male ORB) x 7/16-20 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 7/16-20 (male ORB) x 5/16-24 (female ORB port)</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>7/16-20 (female ORB port)</t>
+          <t>5/16-24 (female ORB port)</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -850,29 +850,34 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1838 Overall Length = 1.100 (table had 1.25); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1838 Hex Flat = 0.625 (table had 0.69) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female -02 ORB port (5/16-24): O-ring chamfer 12deg from dia 0.360 to 0.3248 and minor-bore depth 0.468 measured on the Brennan 6410-04-02-O STEP only (tools/measure/ports.py; ASSUMED, single STEP); port drill D3 = the minor bore measured there (0.270) - no OMi / Air-Way / catalog value for the -02 port drill</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L33 / hex / D from OMi Items (= Brennan TFA p16); male ORB -04 end from the library; female -02 ORB port: no port drill D3 and no measured -02 port geometry yet (own STEP present)</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>6410-04-04-O</t>
+          <t>6410-04-02-O</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6410-04-06-O</t>
+          <t>6410-04-04-O</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="C4" t="n">
-        <v>0.46881</v>
+        <v>0.36084</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.625</v>
       </c>
       <c r="E4" t="n">
         <v>0.21875</v>
@@ -905,55 +910,55 @@
         <v>0.05</v>
       </c>
       <c r="O4" t="n">
-        <v>0.309</v>
+        <v>0.245</v>
       </c>
       <c r="P4" t="n">
         <v>12</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2865</v>
+        <v>0.2233</v>
       </c>
       <c r="R4" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4666</v>
+        <v>0.4116</v>
       </c>
       <c r="T4" t="n">
         <v>60</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="V4" t="n">
-        <v>0.609</v>
+        <v>0.547</v>
       </c>
       <c r="W4" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="X4" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.28007</v>
+        <v>0.21706</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AA4" t="n">
         <v>0.17</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.551</v>
+        <v>0.553</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>6410-04-06-O</t>
+          <t>6410-04-04-O</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 7/16-20 (male ORB) x 9/16-18 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 7/16-20 (male ORB) x 7/16-20 (female ORB port)</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -968,7 +973,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>9/16-18 (female ORB port)</t>
+          <t>7/16-20 (female ORB port)</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -978,110 +983,110 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1839 Overall Length = 1.160 (table had 1.2); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1839 Hex Flat = 0.812 (table had 0.88) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1838 Overall Length = 1.100 (table had 1.25); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1838 Hex Flat = 0.625 (table had 0.69) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6410-04-06-O</t>
+          <t>6410-04-04-O</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6410-06-04-O</t>
+          <t>6410-04-06-O</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="C5" t="n">
-        <v>0.39837</v>
+        <v>0.46881</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.28125</v>
+        <v>0.21875</v>
       </c>
       <c r="F5" t="n">
-        <v>0.312</v>
+        <v>0.265</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2405</v>
+        <v>0.182</v>
       </c>
       <c r="H5" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.312</v>
+        <v>0.265</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="N5" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="O5" t="n">
-        <v>0.245</v>
+        <v>0.309</v>
       </c>
       <c r="P5" t="n">
         <v>12</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2233</v>
+        <v>0.2865</v>
       </c>
       <c r="R5" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4116</v>
+        <v>0.4666</v>
       </c>
       <c r="T5" t="n">
         <v>60</v>
       </c>
       <c r="U5" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="V5" t="n">
-        <v>0.547</v>
+        <v>0.609</v>
       </c>
       <c r="W5" t="n">
-        <v>0.05</v>
+        <v>0.05556</v>
       </c>
       <c r="X5" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.21706</v>
+        <v>0.28007</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.3</v>
+        <v>0.17</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.573</v>
+        <v>0.551</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>6410-06-04-O</t>
+          <t>6410-04-06-O</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 9/16-18 (male ORB) x 7/16-20 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 7/16-20 (male ORB) x 9/16-18 (female ORB port)</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1091,12 +1096,12 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>9/16-18 (male ORB)</t>
+          <t>7/16-20 (male ORB)</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>7/16-20 (female ORB port)</t>
+          <t>9/16-18 (female ORB port)</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -1106,29 +1111,29 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1841 Overall Length = 1.120 (table had 1.03) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1839 Overall Length = 1.160 (table had 1.2); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1839 Hex Flat = 0.812 (table had 0.88) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>6410-06-04-O</t>
+          <t>6410-04-06-O</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6410-06-06-O</t>
+          <t>6410-06-04-O</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="C6" t="n">
-        <v>0.50807</v>
+        <v>0.39837</v>
       </c>
       <c r="D6" t="n">
-        <v>0.88</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E6" t="n">
         <v>0.28125</v>
@@ -1161,55 +1166,55 @@
         <v>0.05556</v>
       </c>
       <c r="O6" t="n">
-        <v>0.309</v>
+        <v>0.245</v>
       </c>
       <c r="P6" t="n">
         <v>12</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2865</v>
+        <v>0.2233</v>
       </c>
       <c r="R6" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4666</v>
+        <v>0.4116</v>
       </c>
       <c r="T6" t="n">
         <v>60</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="V6" t="n">
-        <v>0.609</v>
+        <v>0.547</v>
       </c>
       <c r="W6" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="X6" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.28007</v>
+        <v>0.21706</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AA6" t="n">
         <v>0.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.681</v>
+        <v>0.573</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>6410-06-06-O</t>
+          <t>6410-06-04-O</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 9/16-18 (male ORB) x 9/16-18 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 9/16-18 (male ORB) x 7/16-20 (female ORB port)</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -1224,7 +1229,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>9/16-18 (female ORB port)</t>
+          <t>7/16-20 (female ORB port)</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -1234,23 +1239,23 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1842 Overall Length = 1.290 (table had 1.16) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1841 Overall Length = 1.120 (table had 1.03) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>6410-06-06-O</t>
+          <t>6410-06-04-O</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6410-08-06-O</t>
+          <t>6410-06-06-O</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="C7" t="n">
         <v>0.50807</v>
@@ -1259,34 +1264,34 @@
         <v>0.88</v>
       </c>
       <c r="E7" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="F7" t="n">
-        <v>0.344</v>
+        <v>0.312</v>
       </c>
       <c r="G7" t="n">
-        <v>0.33</v>
+        <v>0.2405</v>
       </c>
       <c r="H7" t="n">
-        <v>0.094</v>
+        <v>0.083</v>
       </c>
       <c r="I7" t="n">
-        <v>0.75</v>
+        <v>0.5625</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="K7" t="n">
-        <v>0.344</v>
+        <v>0.312</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03383</v>
+        <v>0.03007</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01562</v>
+        <v>0.01389</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="O7" t="n">
         <v>0.309</v>
@@ -1322,22 +1327,22 @@
         <v>0.28007</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.551</v>
+        <v>0.681</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>6410-08-06-O</t>
+          <t>6410-06-06-O</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 3/4-16 (male ORB) x 9/16-18 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 9/16-18 (male ORB) x 9/16-18 (female ORB port)</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -1347,7 +1352,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>3/4-16 (male ORB)</t>
+          <t>9/16-18 (male ORB)</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -1362,23 +1367,23 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1842 Overall Length = 1.290 (table had 1.16) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>6410-08-06-O</t>
+          <t>6410-06-06-O</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6410-08-08-O</t>
+          <t>6410-06-08-O</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="C8" t="n">
         <v>0.57735</v>
@@ -1387,34 +1392,34 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="F8" t="n">
-        <v>0.344</v>
+        <v>0.312</v>
       </c>
       <c r="G8" t="n">
-        <v>0.33</v>
+        <v>0.2405</v>
       </c>
       <c r="H8" t="n">
-        <v>0.094</v>
+        <v>0.083</v>
       </c>
       <c r="I8" t="n">
-        <v>0.75</v>
+        <v>0.5625</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="K8" t="n">
-        <v>0.344</v>
+        <v>0.312</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03383</v>
+        <v>0.03007</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01562</v>
+        <v>0.01389</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="O8" t="n">
         <v>0.4065</v>
@@ -1450,22 +1455,22 @@
         <v>0.37383</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.722</v>
+        <v>0.762</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>6410-08-08-O</t>
+          <t>6410-06-08-O</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 3/4-16 (male ORB) x 3/4-16 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 9/16-18 (male ORB) x 3/4-16 (female ORB port)</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -1475,7 +1480,7 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>3/4-16 (male ORB)</t>
+          <t>9/16-18 (male ORB)</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -1490,29 +1495,34 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1846 Overall Length = 1.410 (table had 1.31) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1843 = 1.450 (table had 1.32) | Brennan TFA TFA-p016-t03: agrees on L33@DRIVE, C1HEX@HEX, D@BORE</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>6410-08-08-O</t>
+          <t>6410-06-08-O</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6410-08-10-O</t>
+          <t>6410-08-04-O</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.48</v>
+        <v>1.1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.65241</v>
+        <v>0.50807</v>
       </c>
       <c r="D9" t="n">
-        <v>1.13</v>
+        <v>0.88</v>
       </c>
       <c r="E9" t="n">
         <v>0.375</v>
@@ -1545,55 +1555,55 @@
         <v>0.0625</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4725</v>
+        <v>0.245</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4441</v>
+        <v>0.2233</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4</v>
+        <v>0.19</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6309</v>
+        <v>0.4116</v>
       </c>
       <c r="T9" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8</v>
+        <v>0.38</v>
       </c>
       <c r="V9" t="n">
-        <v>0.781</v>
+        <v>0.547</v>
       </c>
       <c r="W9" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0.4</v>
+        <v>0.19</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.43866</v>
+        <v>0.21706</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.48</v>
+        <v>1.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.699</v>
+        <v>0.553</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>6410-08-10-O</t>
+          <t>6410-08-04-O</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 3/4-16 (male ORB) x 7/8-14 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 3/4-16 (male ORB) x 7/16-20 (female ORB port)</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -1608,7 +1618,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>7/8-14 (female ORB port)</t>
+          <t>7/16-20 (female ORB port)</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
@@ -1618,29 +1628,34 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1847 Overall Length = 1.480 (table had 1.47) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.38 &gt;= port minor 0.38 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.547 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1844 = 1.100 (table had 0.8) | Brennan TFA TFA-p016-t03: agrees on L33@DRIVE, C1HEX@HEX; DIFFERS on D@BORE 0.38 vs Brennan B DRILL 0.391 (built to the dimension source, s6) | DEEP BORE: through-bore 0.38 = port minor 0.3800 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.547 from the port face; the 120deg point would have ended 0.657 deep, 0.443 from the End A tip)</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>6410-08-10-O</t>
+          <t>6410-08-04-O</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6410-08-12-O</t>
+          <t>6410-08-06-O</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.66</v>
+        <v>1.16</v>
       </c>
       <c r="C10" t="n">
-        <v>0.79674</v>
+        <v>0.50807</v>
       </c>
       <c r="D10" t="n">
-        <v>1.38</v>
+        <v>0.88</v>
       </c>
       <c r="E10" t="n">
         <v>0.375</v>
@@ -1673,55 +1688,55 @@
         <v>0.0625</v>
       </c>
       <c r="O10" t="n">
-        <v>0.575</v>
+        <v>0.309</v>
       </c>
       <c r="P10" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.538</v>
+        <v>0.2865</v>
       </c>
       <c r="R10" t="n">
-        <v>0.485</v>
+        <v>0.25</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7149</v>
+        <v>0.4666</v>
       </c>
       <c r="T10" t="n">
         <v>60</v>
       </c>
       <c r="U10" t="n">
-        <v>0.97</v>
+        <v>0.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0.906</v>
+        <v>0.609</v>
       </c>
       <c r="W10" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="X10" t="n">
-        <v>0.485</v>
+        <v>0.25</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.53011</v>
+        <v>0.28007</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.66</v>
+        <v>1.16</v>
       </c>
       <c r="AA10" t="n">
         <v>0.39</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.754</v>
+        <v>0.551</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>6410-08-12-O</t>
+          <t>6410-08-06-O</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 3/4-16 (male ORB) x 1 1/16-12 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 3/4-16 (male ORB) x 9/16-18 (female ORB port)</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -1736,12 +1751,12 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>1 1/16-12 (female ORB port)</t>
+          <t>9/16-18 (female ORB port)</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -1749,20 +1764,25 @@
           <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
         </is>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L33@DRIVE=1.16~1.160; C1HEX@HEX=0.88~0.875; D@BORE=0.39~0.391</t>
+        </is>
+      </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>6410-08-12-O</t>
+          <t>6410-08-06-O</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6410-10-04-O</t>
+          <t>6410-08-08-O</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.93</v>
+        <v>1.41</v>
       </c>
       <c r="C11" t="n">
         <v>0.57735</v>
@@ -1771,85 +1791,85 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="F11" t="n">
-        <v>0.391</v>
+        <v>0.344</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3865</v>
+        <v>0.33</v>
       </c>
       <c r="H11" t="n">
-        <v>0.107</v>
+        <v>0.094</v>
       </c>
       <c r="I11" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="J11" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="K11" t="n">
-        <v>0.391</v>
+        <v>0.344</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03866</v>
+        <v>0.03383</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01786</v>
+        <v>0.01562</v>
       </c>
       <c r="N11" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="O11" t="n">
-        <v>0.245</v>
+        <v>0.4065</v>
       </c>
       <c r="P11" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2233</v>
+        <v>0.378</v>
       </c>
       <c r="R11" t="n">
-        <v>0.19</v>
+        <v>0.34</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4116</v>
+        <v>0.5436</v>
       </c>
       <c r="T11" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="U11" t="n">
-        <v>0.38</v>
+        <v>0.68</v>
       </c>
       <c r="V11" t="n">
-        <v>0.547</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>0.05</v>
+        <v>0.0625</v>
       </c>
       <c r="X11" t="n">
-        <v>0.19</v>
+        <v>0.34</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.21706</v>
+        <v>0.37383</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.93</v>
+        <v>1.41</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.383</v>
+        <v>0.722</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>6410-10-04-O</t>
+          <t>6410-08-08-O</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 7/8-14 (male ORB) x 7/16-20 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 3/4-16 (male ORB) x 3/4-16 (female ORB port)</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -1859,12 +1879,12 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>7/8-14 (male ORB)</t>
+          <t>3/4-16 (male ORB)</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>7/16-20 (female ORB port)</t>
+          <t>3/4-16 (female ORB port)</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
@@ -1874,115 +1894,110 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.38 &gt;= port minor 0.38 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.547 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>OMi Side 1 ID 0.391 NOT applied (2026-09-25): wider than the female port it runs into (-04 port minor 0.38); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | DEEP BORE: through-bore 0.38 = port minor 0.3800 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.547 from the port face; the 120deg point would have ended 0.657 deep, 0.273 from the End A tip); female port reaches 0.383 from the End A tip, inside the End A thread/groove zone (0.498); radial wall there min 0.169 at 0.392 from the tip (OK)</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1846 Overall Length = 1.410 (table had 1.31) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>6410-10-04-O</t>
+          <t>6410-08-08-O</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6410-10-06-O</t>
+          <t>6410-08-10-O</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.93</v>
+        <v>1.48</v>
       </c>
       <c r="C12" t="n">
-        <v>0.57735</v>
+        <v>0.65241</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="F12" t="n">
-        <v>0.391</v>
+        <v>0.344</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3865</v>
+        <v>0.33</v>
       </c>
       <c r="H12" t="n">
-        <v>0.107</v>
+        <v>0.094</v>
       </c>
       <c r="I12" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="J12" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.4725</v>
+      </c>
+      <c r="P12" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.4441</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.6309</v>
+      </c>
+      <c r="T12" t="n">
+        <v>60</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="W12" t="n">
         <v>0.07142999999999999</v>
       </c>
-      <c r="K12" t="n">
-        <v>0.391</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.03866</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.01786</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.07142999999999999</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.309</v>
-      </c>
-      <c r="P12" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.2865</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.4666</v>
-      </c>
-      <c r="T12" t="n">
-        <v>90</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.609</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0.05556</v>
-      </c>
       <c r="X12" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.28007</v>
+        <v>0.43866</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.93</v>
+        <v>1.48</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.321</v>
+        <v>0.699</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>6410-10-06-O</t>
+          <t>6410-08-10-O</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 7/8-14 (male ORB) x 9/16-18 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 3/4-16 (male ORB) x 7/8-14 (female ORB port)</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -1992,12 +2007,12 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>7/8-14 (male ORB)</t>
+          <t>3/4-16 (male ORB)</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>9/16-18 (female ORB port)</t>
+          <t>7/8-14 (female ORB port)</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
@@ -2007,115 +2022,110 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.5 &gt;= port minor 0.5 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.609 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>DEEP BORE: through-bore 0.5 = port minor 0.5000 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.609 from the port face; the 120deg point would have ended 0.753 deep, 0.177 from the End A tip); female port reaches 0.321 from the End A tip, inside the End A thread/groove zone (0.498); radial wall there min 0.106 at 0.392 from the tip (OK)</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1847 Overall Length = 1.480 (table had 1.47) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>6410-10-06-O</t>
+          <t>6410-08-10-O</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6410-10-08-O</t>
+          <t>6410-08-12-O</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.32</v>
+        <v>1.66</v>
       </c>
       <c r="C13" t="n">
-        <v>0.57735</v>
+        <v>0.79674</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="F13" t="n">
-        <v>0.391</v>
+        <v>0.344</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3865</v>
+        <v>0.33</v>
       </c>
       <c r="H13" t="n">
-        <v>0.107</v>
+        <v>0.094</v>
       </c>
       <c r="I13" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="J13" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="K13" t="n">
-        <v>0.391</v>
+        <v>0.344</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03866</v>
+        <v>0.03383</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01786</v>
+        <v>0.01562</v>
       </c>
       <c r="N13" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4065</v>
+        <v>0.575</v>
       </c>
       <c r="P13" t="n">
         <v>15</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.378</v>
+        <v>0.538</v>
       </c>
       <c r="R13" t="n">
-        <v>0.34</v>
+        <v>0.485</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5436</v>
+        <v>0.7149</v>
       </c>
       <c r="T13" t="n">
         <v>60</v>
       </c>
       <c r="U13" t="n">
-        <v>0.68</v>
+        <v>0.97</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.906</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0625</v>
+        <v>0.08333</v>
       </c>
       <c r="X13" t="n">
-        <v>0.34</v>
+        <v>0.485</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.37383</v>
+        <v>0.53011</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.32</v>
+        <v>1.66</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.48</v>
+        <v>0.39</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.632</v>
+        <v>0.754</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>6410-10-08-O</t>
+          <t>6410-08-12-O</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 7/8-14 (male ORB) x 3/4-16 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 3/4-16 (male ORB) x 1 1/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -2125,44 +2135,49 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>7/8-14 (male ORB)</t>
+          <t>3/4-16 (male ORB)</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>3/4-16 (female ORB port)</t>
+          <t>1 1/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1851 Overall Length = 1.320 (table had 1.34) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L33@DRIVE=1.66~1.660; C1HEX@HEX=1.38~1.375; D@BORE=0.39~0.391</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>6410-10-08-O</t>
+          <t>6410-08-12-O</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6410-10-12-O</t>
+          <t>6410-10-04-O</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.79</v>
+        <v>0.93</v>
       </c>
       <c r="C14" t="n">
-        <v>0.79674</v>
+        <v>0.57735</v>
       </c>
       <c r="D14" t="n">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>0.4375</v>
@@ -2195,55 +2210,55 @@
         <v>0.07142999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>0.575</v>
+        <v>0.245</v>
       </c>
       <c r="P14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.538</v>
+        <v>0.2233</v>
       </c>
       <c r="R14" t="n">
-        <v>0.485</v>
+        <v>0.19</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7149</v>
+        <v>0.4116</v>
       </c>
       <c r="T14" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="U14" t="n">
-        <v>0.97</v>
+        <v>0.38</v>
       </c>
       <c r="V14" t="n">
-        <v>0.906</v>
+        <v>0.547</v>
       </c>
       <c r="W14" t="n">
-        <v>0.08333</v>
+        <v>0.05</v>
       </c>
       <c r="X14" t="n">
-        <v>0.485</v>
+        <v>0.19</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.53011</v>
+        <v>0.21706</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.79</v>
+        <v>0.93</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.48</v>
+        <v>0.38</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.884</v>
+        <v>0.383</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>6410-10-12-O</t>
+          <t>6410-10-04-O</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 7/8-14 (male ORB) x 1 1/16-12 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 7/8-14 (male ORB) x 7/16-20 (female ORB port)</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -2258,7 +2273,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>1 1/16-12 (female ORB port)</t>
+          <t>7/16-20 (female ORB port)</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
@@ -2268,110 +2283,115 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1853 Overall Length = 1.790 (table had 1.69) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.38 &gt;= port minor 0.38 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.547 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>OMi Side 1 ID 0.391 NOT applied (2026-09-25): wider than the female port it runs into (-04 port minor 0.38); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | DEEP BORE: through-bore 0.38 = port minor 0.3800 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.547 from the port face; the 120deg point would have ended 0.657 deep, 0.273 from the End A tip); female port reaches 0.383 from the End A tip, inside the End A thread/groove zone (0.498); radial wall there min 0.169 at 0.392 from the tip (OK)</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>6410-10-12-O</t>
+          <t>6410-10-04-O</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6410-12-04-O</t>
+          <t>6410-10-06-O</t>
         </is>
       </c>
       <c r="B15" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.57735</v>
+      </c>
+      <c r="D15" t="n">
         <v>1</v>
       </c>
-      <c r="C15" t="n">
-        <v>0.7216900000000001</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1.25</v>
-      </c>
       <c r="E15" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="F15" t="n">
-        <v>0.469</v>
+        <v>0.391</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4725</v>
+        <v>0.3865</v>
       </c>
       <c r="H15" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="J15" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.469</v>
+        <v>0.391</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="M15" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="N15" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>0.245</v>
+        <v>0.309</v>
       </c>
       <c r="P15" t="n">
         <v>12</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.2233</v>
+        <v>0.2865</v>
       </c>
       <c r="R15" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4116</v>
+        <v>0.4666</v>
       </c>
       <c r="T15" t="n">
         <v>90</v>
       </c>
       <c r="U15" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="V15" t="n">
-        <v>0.547</v>
+        <v>0.609</v>
       </c>
       <c r="W15" t="n">
-        <v>0.05</v>
+        <v>0.05556</v>
       </c>
       <c r="X15" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.21706</v>
+        <v>0.28007</v>
       </c>
       <c r="Z15" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.453</v>
+        <v>0.321</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>6410-12-04-O</t>
+          <t>6410-10-06-O</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 1/16-12 (male ORB) x 7/16-20 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 7/8-14 (male ORB) x 9/16-18 (female ORB port)</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
@@ -2381,130 +2401,130 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>1 1/16-12 (male ORB)</t>
+          <t>7/8-14 (male ORB)</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>7/16-20 (female ORB port)</t>
+          <t>9/16-18 (female ORB port)</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.38 &gt;= port minor 0.38 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.547 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.5 &gt;= port minor 0.5 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.609 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>DEEP BORE: through-bore 0.38 = port minor 0.3800 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.547 from the port face; the 120deg point would have ended 0.657 deep, 0.343 from the End A tip); female port reaches 0.453 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.255 at 0.469 from the tip (OK)</t>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L33@DRIVE=0.93~0.930; C1HEX@HEX=1~1.000; D@BORE=0.5~0.508 | DEEP BORE: through-bore 0.5 = port minor 0.5000 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.609 from the port face; the 120deg point would have ended 0.753 deep, 0.177 from the End A tip); female port reaches 0.321 from the End A tip, inside the End A thread/groove zone (0.498); radial wall there min 0.106 at 0.392 from the tip (OK)</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>6410-12-04-O</t>
+          <t>6410-10-06-O</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6410-12-06-O</t>
+          <t>6410-10-08-O</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.57735</v>
       </c>
       <c r="D16" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="F16" t="n">
-        <v>0.469</v>
+        <v>0.391</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4725</v>
+        <v>0.3865</v>
       </c>
       <c r="H16" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="J16" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.469</v>
+        <v>0.391</v>
       </c>
       <c r="L16" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="M16" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="N16" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>0.309</v>
+        <v>0.4065</v>
       </c>
       <c r="P16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.2865</v>
+        <v>0.378</v>
       </c>
       <c r="R16" t="n">
-        <v>0.25</v>
+        <v>0.34</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4666</v>
+        <v>0.5436</v>
       </c>
       <c r="T16" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
       <c r="V16" t="n">
-        <v>0.609</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>0.05556</v>
+        <v>0.0625</v>
       </c>
       <c r="X16" t="n">
-        <v>0.25</v>
+        <v>0.34</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.28007</v>
+        <v>0.37383</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.481</v>
+        <v>0.632</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>6410-12-06-O</t>
+          <t>6410-10-08-O</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 1/16-12 (male ORB) x 9/16-18 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 7/8-14 (male ORB) x 3/4-16 (female ORB port)</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
@@ -2514,12 +2534,12 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>1 1/16-12 (male ORB)</t>
+          <t>7/8-14 (male ORB)</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>9/16-18 (female ORB port)</t>
+          <t>3/4-16 (female ORB port)</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
@@ -2529,115 +2549,110 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.5 &gt;= port minor 0.5 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.609 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>OMi Side 1 ID 0.609 NOT applied (2026-09-25): wider than the female port it runs into (-06 port minor 0.50); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | DEEP BORE: through-bore 0.5 = port minor 0.5000 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.609 from the port face; the 120deg point would have ended 0.753 deep, 0.337 from the End A tip); female port reaches 0.481 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.192 at 0.481 from the tip (OK)</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1851 Overall Length = 1.320 (table had 1.34) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>6410-12-06-O</t>
+          <t>6410-10-08-O</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6410-12-10-O</t>
+          <t>6410-10-12-O</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.79674</v>
       </c>
       <c r="D17" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="E17" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="F17" t="n">
-        <v>0.469</v>
+        <v>0.391</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4725</v>
+        <v>0.3865</v>
       </c>
       <c r="H17" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="J17" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.469</v>
+        <v>0.391</v>
       </c>
       <c r="L17" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="M17" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="N17" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4725</v>
+        <v>0.575</v>
       </c>
       <c r="P17" t="n">
         <v>15</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.4441</v>
+        <v>0.538</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4</v>
+        <v>0.485</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6309</v>
+        <v>0.7149</v>
       </c>
       <c r="T17" t="n">
         <v>60</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8</v>
+        <v>0.97</v>
       </c>
       <c r="V17" t="n">
-        <v>0.781</v>
+        <v>0.906</v>
       </c>
       <c r="W17" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.08333</v>
       </c>
       <c r="X17" t="n">
-        <v>0.4</v>
+        <v>0.485</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.43866</v>
+        <v>0.53011</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.699</v>
+        <v>0.884</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>6410-12-10-O</t>
+          <t>6410-10-12-O</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 1/16-12 (male ORB) x 7/8-14 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 7/8-14 (male ORB) x 1 1/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
@@ -2647,12 +2662,12 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>1 1/16-12 (male ORB)</t>
+          <t>7/8-14 (male ORB)</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>7/8-14 (female ORB port)</t>
+          <t>1 1/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -2662,29 +2677,29 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1857 Overall Length = 1.480 (table had 1.56) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1853 Overall Length = 1.790 (table had 1.69) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>6410-12-10-O</t>
+          <t>6410-10-12-O</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6410-12-12-O</t>
+          <t>6410-12-04-O</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.83</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0.79674</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="E18" t="n">
         <v>0.53125</v>
@@ -2717,55 +2732,55 @@
         <v>0.08333</v>
       </c>
       <c r="O18" t="n">
-        <v>0.575</v>
+        <v>0.245</v>
       </c>
       <c r="P18" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.538</v>
+        <v>0.2233</v>
       </c>
       <c r="R18" t="n">
-        <v>0.485</v>
+        <v>0.19</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7149</v>
+        <v>0.4116</v>
       </c>
       <c r="T18" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="U18" t="n">
-        <v>0.97</v>
+        <v>0.38</v>
       </c>
       <c r="V18" t="n">
-        <v>0.906</v>
+        <v>0.547</v>
       </c>
       <c r="W18" t="n">
-        <v>0.08333</v>
+        <v>0.05</v>
       </c>
       <c r="X18" t="n">
-        <v>0.485</v>
+        <v>0.19</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.53011</v>
+        <v>0.21706</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.83</v>
+        <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.61</v>
+        <v>0.38</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.924</v>
+        <v>0.453</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>6410-12-12-O</t>
+          <t>6410-12-04-O</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 1/16-12 (male ORB) x 1 1/16-12 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 1/16-12 (male ORB) x 7/16-20 (female ORB port)</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
@@ -2780,39 +2795,44 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>1 1/16-12 (female ORB port)</t>
+          <t>7/16-20 (female ORB port)</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1858 Overall Length = 1.830 (table had 1.75) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.38 &gt;= port minor 0.38 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.547 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.0 (Lengths to check!E4; website file said 1.000, a filler) = the Air-Way L33 1 already in this row -&gt; no change; OMi and Air-Way agree on the length | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L33@DRIVE=1~1.000; C1HEX@HEX=1.25~1.250; D@BORE=0.38~0.389 | DEEP BORE: through-bore 0.38 = port minor 0.3800 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.547 from the port face; the 120deg point would have ended 0.657 deep, 0.343 from the End A tip); female port reaches 0.453 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.255 at 0.469 from the tip (OK)</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>6410-12-12-O</t>
+          <t>6410-12-04-O</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6410-12-16-O</t>
+          <t>6410-12-06-O</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.92</v>
+        <v>1.09</v>
       </c>
       <c r="C19" t="n">
-        <v>0.94108</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="E19" t="n">
         <v>0.53125</v>
@@ -2845,55 +2865,55 @@
         <v>0.08333</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7</v>
+        <v>0.309</v>
       </c>
       <c r="P19" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.663</v>
+        <v>0.2865</v>
       </c>
       <c r="R19" t="n">
-        <v>0.61</v>
+        <v>0.25</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7149</v>
+        <v>0.4666</v>
       </c>
       <c r="T19" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="U19" t="n">
-        <v>1.22</v>
+        <v>0.5</v>
       </c>
       <c r="V19" t="n">
-        <v>0.906</v>
+        <v>0.609</v>
       </c>
       <c r="W19" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="X19" t="n">
-        <v>0.61</v>
+        <v>0.25</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.65511</v>
+        <v>0.28007</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.92</v>
+        <v>1.09</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.61</v>
+        <v>0.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.014</v>
+        <v>0.481</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>6410-12-16-O</t>
+          <t>6410-12-06-O</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 1/16-12 (male ORB) x 1 5/16-12 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 1/16-12 (male ORB) x 9/16-18 (female ORB port)</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
@@ -2908,7 +2928,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>1 5/16-12 (female ORB port)</t>
+          <t>9/16-18 (female ORB port)</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
@@ -2918,44 +2938,49 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1859 Overall Length = 1.920 (table had 1.88) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.5 &gt;= port minor 0.5 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.609 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>OMi Side 1 ID 0.609 NOT applied (2026-09-25): wider than the female port it runs into (-06 port minor 0.50); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | DEEP BORE: through-bore 0.5 = port minor 0.5000 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.609 from the port face; the 120deg point would have ended 0.753 deep, 0.337 from the End A tip); female port reaches 0.481 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.192 at 0.481 from the tip (OK)</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>6410-12-16-O</t>
+          <t>6410-12-06-O</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6410-16-06-O</t>
+          <t>6410-12-10-O</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>1.48</v>
       </c>
       <c r="C20" t="n">
-        <v>0.86603</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="E20" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="F20" t="n">
         <v>0.469</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5975</v>
+        <v>0.4725</v>
       </c>
       <c r="H20" t="n">
         <v>0.125</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="J20" t="n">
         <v>0.08333</v>
@@ -2973,55 +2998,55 @@
         <v>0.08333</v>
       </c>
       <c r="O20" t="n">
-        <v>0.309</v>
+        <v>0.4725</v>
       </c>
       <c r="P20" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.2865</v>
+        <v>0.4441</v>
       </c>
       <c r="R20" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4666</v>
+        <v>0.6309</v>
       </c>
       <c r="T20" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="V20" t="n">
-        <v>0.609</v>
+        <v>0.781</v>
       </c>
       <c r="W20" t="n">
-        <v>0.05556</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="X20" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.28007</v>
+        <v>0.43866</v>
       </c>
       <c r="Z20" t="n">
-        <v>1</v>
+        <v>1.48</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.5</v>
+        <v>0.61</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.391</v>
+        <v>0.699</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>6410-16-06-O</t>
+          <t>6410-12-10-O</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/16-12 (male ORB) x 9/16-18 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 1/16-12 (male ORB) x 7/8-14 (female ORB port)</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
@@ -3031,12 +3056,12 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>1 5/16-12 (male ORB)</t>
+          <t>1 1/16-12 (male ORB)</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>9/16-18 (female ORB port)</t>
+          <t>7/8-14 (female ORB port)</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
@@ -3046,49 +3071,44 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.5 &gt;= port minor 0.5 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.609 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>DEEP BORE: through-bore 0.5 = port minor 0.5000 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.609 from the port face; the 120deg point would have ended 0.753 deep, 0.247 from the End A tip); female port reaches 0.391 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.317 at 0.469 from the tip (OK)</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1857 Overall Length = 1.480 (table had 1.56) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>6410-16-06-O</t>
+          <t>6410-12-10-O</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6410-16-08-O</t>
+          <t>6410-12-12-O</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.12</v>
+        <v>1.83</v>
       </c>
       <c r="C21" t="n">
-        <v>0.86603</v>
+        <v>0.79674</v>
       </c>
       <c r="D21" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="E21" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="F21" t="n">
         <v>0.469</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5975</v>
+        <v>0.4725</v>
       </c>
       <c r="H21" t="n">
         <v>0.125</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="J21" t="n">
         <v>0.08333</v>
@@ -3106,55 +3126,55 @@
         <v>0.08333</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4065</v>
+        <v>0.575</v>
       </c>
       <c r="P21" t="n">
         <v>15</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.378</v>
+        <v>0.538</v>
       </c>
       <c r="R21" t="n">
-        <v>0.34</v>
+        <v>0.485</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5436</v>
+        <v>0.7149</v>
       </c>
       <c r="T21" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="U21" t="n">
-        <v>0.68</v>
+        <v>0.97</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.906</v>
       </c>
       <c r="W21" t="n">
-        <v>0.0625</v>
+        <v>0.08333</v>
       </c>
       <c r="X21" t="n">
-        <v>0.34</v>
+        <v>0.485</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.37383</v>
+        <v>0.53011</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.12</v>
+        <v>1.83</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.432</v>
+        <v>0.924</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>6410-16-08-O</t>
+          <t>6410-12-12-O</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/16-12 (male ORB) x 3/4-16 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 1/16-12 (male ORB) x 1 1/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
@@ -3164,12 +3184,12 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>1 5/16-12 (male ORB)</t>
+          <t>1 1/16-12 (male ORB)</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>3/4-16 (female ORB port)</t>
+          <t>1 1/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
@@ -3179,49 +3199,44 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.68 &gt;= port minor 0.68 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.688 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>DEEP BORE: through-bore 0.68 = port minor 0.6800 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.688 from the port face; the 120deg point would have ended 0.884 deep, 0.236 from the End A tip); female port reaches 0.432 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.224 at 0.469 from the tip (OK)</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1858 Overall Length = 1.830 (table had 1.75) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>6410-16-08-O</t>
+          <t>6410-12-12-O</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6410-16-10-O</t>
+          <t>6410-12-16-O</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="C22" t="n">
-        <v>0.86603</v>
+        <v>0.94108</v>
       </c>
       <c r="D22" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="E22" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="F22" t="n">
         <v>0.469</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5975</v>
+        <v>0.4725</v>
       </c>
       <c r="H22" t="n">
         <v>0.125</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="J22" t="n">
         <v>0.08333</v>
@@ -3239,55 +3254,55 @@
         <v>0.08333</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4725</v>
+        <v>0.7</v>
       </c>
       <c r="P22" t="n">
         <v>15</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.4441</v>
+        <v>0.663</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4</v>
+        <v>0.61</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6309</v>
+        <v>0.7149</v>
       </c>
       <c r="T22" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8</v>
+        <v>1.22</v>
       </c>
       <c r="V22" t="n">
-        <v>0.781</v>
+        <v>0.906</v>
       </c>
       <c r="W22" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.08333</v>
       </c>
       <c r="X22" t="n">
-        <v>0.4</v>
+        <v>0.61</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.43866</v>
+        <v>0.65511</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.8</v>
+        <v>0.61</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.789</v>
+        <v>1.014</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>6410-16-10-O</t>
+          <t>6410-12-16-O</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/16-12 (male ORB) x 7/8-14 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 1/16-12 (male ORB) x 1 5/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
@@ -3297,12 +3312,12 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>1 5/16-12 (male ORB)</t>
+          <t>1 1/16-12 (male ORB)</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>7/8-14 (female ORB port)</t>
+          <t>1 5/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
@@ -3312,28 +3327,23 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1865 Overall Length = 1.570 (table had 1.12) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.8 &gt;= port minor 0.8 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.781 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>DEEP BORE: through-bore 0.8 = port minor 0.8000 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.781 from the port face; the 120deg point would have ended 1.012 deep, 0.558 from the End A tip)</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1859 Overall Length = 1.920 (table had 1.88) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>6410-16-10-O</t>
+          <t>6410-12-16-O</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6410-16-12-O</t>
+          <t>6410-16-04-O</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.71</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
         <v>0.86603</v>
@@ -3372,55 +3382,55 @@
         <v>0.08333</v>
       </c>
       <c r="O23" t="n">
-        <v>0.575</v>
+        <v>0.245</v>
       </c>
       <c r="P23" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.538</v>
+        <v>0.2233</v>
       </c>
       <c r="R23" t="n">
-        <v>0.485</v>
+        <v>0.19</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7149</v>
+        <v>0.4116</v>
       </c>
       <c r="T23" t="n">
         <v>60</v>
       </c>
       <c r="U23" t="n">
-        <v>0.97</v>
+        <v>0.38</v>
       </c>
       <c r="V23" t="n">
-        <v>0.906</v>
+        <v>0.547</v>
       </c>
       <c r="W23" t="n">
-        <v>0.08333</v>
+        <v>0.05</v>
       </c>
       <c r="X23" t="n">
-        <v>0.485</v>
+        <v>0.19</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.53011</v>
+        <v>0.21706</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.71</v>
+        <v>1</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.84</v>
+        <v>0.368</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.804</v>
+        <v>0.453</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>6410-16-12-O</t>
+          <t>6410-16-04-O</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/16-12 (male ORB) x 1 1/16-12 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/16-12 (male ORB) x 7/16-20 (female ORB port)</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
@@ -3435,39 +3445,44 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>1 1/16-12 (female ORB port)</t>
+          <t>7/16-20 (female ORB port)</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1866 Overall Length = 1.710 (table had 1.7) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): L33 = OMi real length (Lengths to check!E5); hex / Side 1 ID OMi website file Items row 1862; ORB end values from the end library (Q-TRANSFER-ENDLIB); user 2026-10-18: "this is verified information, use it"; one source -&gt; ASSUMED | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): website length 1.000 was a filler; OMi gave 1.0 | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified) | female port reaches 0.343 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.380 at 0.469 from the tip (OK)</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>6410-16-12-O</t>
+          <t>6410-16-04-O</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6410-16-16-O</t>
+          <t>6410-16-06-O</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.81</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0.94108</v>
+        <v>0.86603</v>
       </c>
       <c r="D24" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="E24" t="n">
         <v>0.65625</v>
@@ -3500,55 +3515,55 @@
         <v>0.08333</v>
       </c>
       <c r="O24" t="n">
-        <v>0.7</v>
+        <v>0.309</v>
       </c>
       <c r="P24" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.663</v>
+        <v>0.2865</v>
       </c>
       <c r="R24" t="n">
-        <v>0.61</v>
+        <v>0.25</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7149</v>
+        <v>0.4666</v>
       </c>
       <c r="T24" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="U24" t="n">
-        <v>1.22</v>
+        <v>0.5</v>
       </c>
       <c r="V24" t="n">
-        <v>0.906</v>
+        <v>0.609</v>
       </c>
       <c r="W24" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="X24" t="n">
-        <v>0.61</v>
+        <v>0.25</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.65511</v>
+        <v>0.28007</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.81</v>
+        <v>1</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.84</v>
+        <v>0.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.904</v>
+        <v>0.391</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>6410-16-16-O</t>
+          <t>6410-16-06-O</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/16-12 (male ORB) x 1 5/16-12 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/16-12 (male ORB) x 9/16-18 (female ORB port)</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
@@ -3563,44 +3578,44 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>1 5/16-12 (female ORB port)</t>
+          <t>9/16-18 (female ORB port)</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1868 Overall Length = 1.81 (table had 1.97) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.5 &gt;= port minor 0.5 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.609 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>B(2) printed "1 1/16-12" both passes (a -16 female end is 1 5/16-12; L33/C1/D3 progression supports -16) - as-printed, likely typo</t>
+          <t>OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.0 (Lengths to check!E6; website file said 1.000, a filler) = the Air-Way L33 1 already in this row -&gt; no change; OMi and Air-Way agree on the length | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L33@DRIVE=1~1.000; C1HEX@HEX=1.5~1.500; D@BORE=0.5~0.508 | DEEP BORE: through-bore 0.5 = port minor 0.5000 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.609 from the port face; the 120deg point would have ended 0.753 deep, 0.247 from the End A tip); female port reaches 0.391 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.317 at 0.469 from the tip (OK)</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>6410-16-16-O</t>
+          <t>6410-16-06-O</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6410-16-20-O</t>
+          <t>6410-16-08-O</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.14</v>
+        <v>1.12</v>
       </c>
       <c r="C25" t="n">
-        <v>1.22687</v>
+        <v>0.86603</v>
       </c>
       <c r="D25" t="n">
-        <v>2.125</v>
+        <v>1.5</v>
       </c>
       <c r="E25" t="n">
         <v>0.65625</v>
@@ -3633,55 +3648,55 @@
         <v>0.08333</v>
       </c>
       <c r="O25" t="n">
-        <v>0.8575</v>
+        <v>0.4065</v>
       </c>
       <c r="P25" t="n">
         <v>15</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.8205</v>
+        <v>0.378</v>
       </c>
       <c r="R25" t="n">
-        <v>0.765</v>
+        <v>0.34</v>
       </c>
       <c r="S25" t="n">
-        <v>0.7124</v>
+        <v>0.5436</v>
       </c>
       <c r="T25" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="U25" t="n">
-        <v>1.53</v>
+        <v>0.68</v>
       </c>
       <c r="V25" t="n">
-        <v>0.906</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="X25" t="n">
-        <v>0.765</v>
+        <v>0.34</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.81011</v>
+        <v>0.37383</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.14</v>
+        <v>1.12</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.84</v>
+        <v>0.68</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.234</v>
+        <v>0.432</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>6410-16-20-O</t>
+          <t>6410-16-08-O</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/16-12 (male ORB) x 1 5/8-12 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/16-12 (male ORB) x 3/4-16 (female ORB port)</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
@@ -3696,7 +3711,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>1 5/8-12 (female ORB port)</t>
+          <t>3/4-16 (female ORB port)</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
@@ -3706,44 +3721,49 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1869 Overall Length = 2.140 (table had 2); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1869 Hex Flat = 2.125 (table had 2) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.68 &gt;= port minor 0.68 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.688 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.12 (Lengths to check!E7; website file said 1.000, a filler) = the Air-Way L33 1.12 already in this row -&gt; no change; OMi and Air-Way agree on the length | DEEP BORE: through-bore 0.68 = port minor 0.6800 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.688 from the port face; the 120deg point would have ended 0.884 deep, 0.236 from the End A tip); female port reaches 0.432 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.224 at 0.469 from the tip (OK)</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>6410-16-20-O</t>
+          <t>6410-16-08-O</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6410-20-12-O</t>
+          <t>6410-16-10-O</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="C26" t="n">
-        <v>1.08542</v>
+        <v>0.86603</v>
       </c>
       <c r="D26" t="n">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="F26" t="n">
         <v>0.469</v>
       </c>
       <c r="G26" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.5975</v>
       </c>
       <c r="H26" t="n">
         <v>0.125</v>
       </c>
       <c r="I26" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="J26" t="n">
         <v>0.08333</v>
@@ -3761,55 +3781,55 @@
         <v>0.08333</v>
       </c>
       <c r="O26" t="n">
-        <v>0.575</v>
+        <v>0.4725</v>
       </c>
       <c r="P26" t="n">
         <v>15</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.538</v>
+        <v>0.4441</v>
       </c>
       <c r="R26" t="n">
-        <v>0.485</v>
+        <v>0.4</v>
       </c>
       <c r="S26" t="n">
-        <v>0.7149</v>
+        <v>0.6309</v>
       </c>
       <c r="T26" t="n">
         <v>90</v>
       </c>
       <c r="U26" t="n">
-        <v>0.97</v>
+        <v>0.8</v>
       </c>
       <c r="V26" t="n">
-        <v>0.906</v>
+        <v>0.781</v>
       </c>
       <c r="W26" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="X26" t="n">
-        <v>0.485</v>
+        <v>0.4</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.53011</v>
+        <v>0.43866</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.97</v>
+        <v>0.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.294</v>
+        <v>0.789</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>6410-20-12-O</t>
+          <t>6410-16-10-O</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/8-12 (male ORB) x 1 1/16-12 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/16-12 (male ORB) x 7/8-14 (female ORB port)</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
@@ -3819,12 +3839,12 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>1 5/8-12 (male ORB)</t>
+          <t>1 5/16-12 (male ORB)</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>1 1/16-12 (female ORB port)</t>
+          <t>7/8-14 (female ORB port)</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
@@ -3834,49 +3854,49 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.97 &gt;= port minor 0.97 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.906 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1865 Overall Length = 1.570 (table had 1.12) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.8 &gt;= port minor 0.8 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.781 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>OMi Side 1 ID 0.981 NOT applied (2026-09-25): wider than the female port it runs into (-12 port minor 0.97); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | DEEP BORE: through-bore 0.97 = port minor 0.9700 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.906 from the port face; the 120deg point would have ended 1.186 deep, 0.014 from the End A tip); female port reaches 0.294 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.223 at 0.469 from the tip (OK)</t>
+          <t>DEEP BORE: through-bore 0.8 = port minor 0.8000 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.781 from the port face; the 120deg point would have ended 1.012 deep, 0.558 from the End A tip)</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>6410-20-12-O</t>
+          <t>6410-16-10-O</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6410-20-16-O</t>
+          <t>6410-16-12-O</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.2</v>
+        <v>1.71</v>
       </c>
       <c r="C27" t="n">
-        <v>1.08542</v>
+        <v>0.86603</v>
       </c>
       <c r="D27" t="n">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="F27" t="n">
         <v>0.469</v>
       </c>
       <c r="G27" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.5975</v>
       </c>
       <c r="H27" t="n">
         <v>0.125</v>
       </c>
       <c r="I27" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="J27" t="n">
         <v>0.08333</v>
@@ -3894,25 +3914,25 @@
         <v>0.08333</v>
       </c>
       <c r="O27" t="n">
-        <v>0.7</v>
+        <v>0.575</v>
       </c>
       <c r="P27" t="n">
         <v>15</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.663</v>
+        <v>0.538</v>
       </c>
       <c r="R27" t="n">
-        <v>0.61</v>
+        <v>0.485</v>
       </c>
       <c r="S27" t="n">
         <v>0.7149</v>
       </c>
       <c r="T27" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="U27" t="n">
-        <v>1.22</v>
+        <v>0.97</v>
       </c>
       <c r="V27" t="n">
         <v>0.906</v>
@@ -3921,28 +3941,28 @@
         <v>0.08333</v>
       </c>
       <c r="X27" t="n">
-        <v>0.61</v>
+        <v>0.485</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.65511</v>
+        <v>0.53011</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.2</v>
+        <v>1.71</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.22</v>
+        <v>0.84</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.294</v>
+        <v>0.804</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>6410-20-16-O</t>
+          <t>6410-16-12-O</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/8-12 (male ORB) x 1 5/16-12 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/16-12 (male ORB) x 1 1/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
@@ -3952,12 +3972,12 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>1 5/8-12 (male ORB)</t>
+          <t>1 5/16-12 (male ORB)</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>1 5/16-12 (female ORB port)</t>
+          <t>1 1/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
@@ -3967,49 +3987,44 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 1.22 &gt;= port minor 1.22 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.906 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>OMi Side 1 ID 1.231 NOT applied (2026-09-25): wider than the female port it runs into (-16 port minor 1.22); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | DEEP BORE: through-bore 1.22 = port minor 1.2200 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.906 from the port face; the 120deg point would have ended 1.258 deep, -0.058 from the End A tip); female port reaches 0.294 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.098 at 0.469 from the tip (OK)</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1866 Overall Length = 1.710 (table had 1.7) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>6410-20-16-O</t>
+          <t>6410-16-12-O</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6410-20-24-O</t>
+          <t>6410-16-16-O</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="C28" t="n">
-        <v>1.29904</v>
+        <v>0.94108</v>
       </c>
       <c r="D28" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="E28" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="F28" t="n">
         <v>0.469</v>
       </c>
       <c r="G28" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.5975</v>
       </c>
       <c r="H28" t="n">
         <v>0.125</v>
       </c>
       <c r="I28" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="J28" t="n">
         <v>0.08333</v>
@@ -4027,25 +4042,25 @@
         <v>0.08333</v>
       </c>
       <c r="O28" t="n">
-        <v>0.983</v>
+        <v>0.7</v>
       </c>
       <c r="P28" t="n">
         <v>15</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.946</v>
+        <v>0.663</v>
       </c>
       <c r="R28" t="n">
-        <v>0.89</v>
+        <v>0.61</v>
       </c>
       <c r="S28" t="n">
-        <v>0.7119</v>
+        <v>0.7149</v>
       </c>
       <c r="T28" t="n">
         <v>60</v>
       </c>
       <c r="U28" t="n">
-        <v>1.78</v>
+        <v>1.22</v>
       </c>
       <c r="V28" t="n">
         <v>0.906</v>
@@ -4054,28 +4069,28 @@
         <v>0.08333</v>
       </c>
       <c r="X28" t="n">
-        <v>0.89</v>
+        <v>0.61</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.93511</v>
+        <v>0.65511</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.074</v>
+        <v>0.904</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>6410-20-24-O</t>
+          <t>6410-16-16-O</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/8-12 (male ORB) x 1 7/8-12 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/16-12 (male ORB) x 1 5/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
@@ -4085,12 +4100,12 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>1 5/8-12 (male ORB)</t>
+          <t>1 5/16-12 (male ORB)</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>1 7/8-12 (female ORB port)</t>
+          <t>1 5/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
@@ -4100,44 +4115,49 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1874 Overall Length = 1.980 (table had 1.88) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1868 Overall Length = 1.81 (table had 1.97) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>B(2) printed "1 1/16-12" both passes (a -16 female end is 1 5/16-12; L33/C1/D3 progression supports -16) - as-printed, likely typo</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>6410-20-24-O</t>
+          <t>6410-16-16-O</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6410-24-12-O</t>
+          <t>6410-16-20-O</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.26</v>
+        <v>2.14</v>
       </c>
       <c r="C29" t="n">
-        <v>1.22976</v>
+        <v>1.22687</v>
       </c>
       <c r="D29" t="n">
-        <v>2.13</v>
+        <v>2.125</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9375</v>
+        <v>0.65625</v>
       </c>
       <c r="F29" t="n">
         <v>0.469</v>
       </c>
       <c r="G29" t="n">
-        <v>0.878</v>
+        <v>0.5975</v>
       </c>
       <c r="H29" t="n">
         <v>0.125</v>
       </c>
       <c r="I29" t="n">
-        <v>1.875</v>
+        <v>1.3125</v>
       </c>
       <c r="J29" t="n">
         <v>0.08333</v>
@@ -4155,25 +4175,25 @@
         <v>0.08333</v>
       </c>
       <c r="O29" t="n">
-        <v>0.575</v>
+        <v>0.8575</v>
       </c>
       <c r="P29" t="n">
         <v>15</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.538</v>
+        <v>0.8205</v>
       </c>
       <c r="R29" t="n">
-        <v>0.485</v>
+        <v>0.765</v>
       </c>
       <c r="S29" t="n">
-        <v>0.7149</v>
+        <v>0.7124</v>
       </c>
       <c r="T29" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="U29" t="n">
-        <v>0.97</v>
+        <v>1.53</v>
       </c>
       <c r="V29" t="n">
         <v>0.906</v>
@@ -4182,28 +4202,28 @@
         <v>0.08333</v>
       </c>
       <c r="X29" t="n">
-        <v>0.485</v>
+        <v>0.765</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.53011</v>
+        <v>0.81011</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.26</v>
+        <v>2.14</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.97</v>
+        <v>0.84</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.354</v>
+        <v>1.234</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>6410-24-12-O</t>
+          <t>6410-16-20-O</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 7/8-12 (male ORB) x 1 1/16-12 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/16-12 (male ORB) x 1 5/8-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
@@ -4213,12 +4233,12 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>1 7/8-12 (male ORB)</t>
+          <t>1 5/16-12 (male ORB)</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>1 1/16-12 (female ORB port)</t>
+          <t>1 5/8-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
@@ -4228,49 +4248,44 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.97 &gt;= port minor 0.97 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.906 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>OMi Side 1 ID 0.981 NOT applied (2026-09-25): wider than the female port it runs into (-12 port minor 0.97); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | DEEP BORE: through-bore 0.97 = port minor 0.9700 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.906 from the port face; the 120deg point would have ended 1.186 deep, 0.074 from the End A tip); female port reaches 0.354 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.348 at 0.469 from the tip (OK)</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1869 Overall Length = 2.140 (table had 2); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1869 Hex Flat = 2.125 (table had 2) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>6410-24-12-O</t>
+          <t>6410-16-20-O</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6410-24-16-O</t>
+          <t>6410-20-12-O</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="C30" t="n">
-        <v>1.22976</v>
+        <v>1.08542</v>
       </c>
       <c r="D30" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="F30" t="n">
         <v>0.469</v>
       </c>
       <c r="G30" t="n">
-        <v>0.878</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="H30" t="n">
         <v>0.125</v>
       </c>
       <c r="I30" t="n">
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
       <c r="J30" t="n">
         <v>0.08333</v>
@@ -4288,16 +4303,16 @@
         <v>0.08333</v>
       </c>
       <c r="O30" t="n">
-        <v>0.7</v>
+        <v>0.575</v>
       </c>
       <c r="P30" t="n">
         <v>15</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.663</v>
+        <v>0.538</v>
       </c>
       <c r="R30" t="n">
-        <v>0.61</v>
+        <v>0.485</v>
       </c>
       <c r="S30" t="n">
         <v>0.7149</v>
@@ -4306,7 +4321,7 @@
         <v>90</v>
       </c>
       <c r="U30" t="n">
-        <v>1.22</v>
+        <v>0.97</v>
       </c>
       <c r="V30" t="n">
         <v>0.906</v>
@@ -4315,28 +4330,28 @@
         <v>0.08333</v>
       </c>
       <c r="X30" t="n">
-        <v>0.61</v>
+        <v>0.485</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.65511</v>
+        <v>0.53011</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.22</v>
+        <v>0.97</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.364</v>
+        <v>0.294</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>6410-24-16-O</t>
+          <t>6410-20-12-O</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 7/8-12 (male ORB) x 1 5/16-12 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/8-12 (male ORB) x 1 1/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
@@ -4346,12 +4361,12 @@
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>1 7/8-12 (male ORB)</t>
+          <t>1 5/8-12 (male ORB)</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>1 5/16-12 (female ORB port)</t>
+          <t>1 1/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
@@ -4361,49 +4376,49 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 1.22 &gt;= port minor 1.22 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.906 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.97 &gt;= port minor 0.97 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.906 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>OMi Side 1 ID 1.231 NOT applied (2026-09-25): wider than the female port it runs into (-16 port minor 1.22); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | DEEP BORE: through-bore 1.22 = port minor 1.2200 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.906 from the port face; the 120deg point would have ended 1.258 deep, 0.012 from the End A tip); female port reaches 0.364 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.223 at 0.469 from the tip (OK)</t>
+          <t>OMi Side 1 ID 0.981 NOT applied (2026-09-25): wider than the female port it runs into (-12 port minor 0.97); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.2 (Lengths to check!E10; website file said 1.000, a filler) = the Air-Way L33 1.2 already in this row -&gt; no change; OMi and Air-Way agree on the length | DEEP BORE: through-bore 0.97 = port minor 0.9700 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.906 from the port face; the 120deg point would have ended 1.186 deep, 0.014 from the End A tip); female port reaches 0.294 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.223 at 0.469 from the tip (OK)</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>6410-24-16-O</t>
+          <t>6410-20-12-O</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6410-24-20-O</t>
+          <t>6410-20-16-O</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.75</v>
+        <v>1.2</v>
       </c>
       <c r="C31" t="n">
-        <v>1.22976</v>
+        <v>1.08542</v>
       </c>
       <c r="D31" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="F31" t="n">
         <v>0.469</v>
       </c>
       <c r="G31" t="n">
-        <v>0.878</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="H31" t="n">
         <v>0.125</v>
       </c>
       <c r="I31" t="n">
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
       <c r="J31" t="n">
         <v>0.08333</v>
@@ -4421,25 +4436,25 @@
         <v>0.08333</v>
       </c>
       <c r="O31" t="n">
-        <v>0.8575</v>
+        <v>0.7</v>
       </c>
       <c r="P31" t="n">
         <v>15</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.8205</v>
+        <v>0.663</v>
       </c>
       <c r="R31" t="n">
-        <v>0.765</v>
+        <v>0.61</v>
       </c>
       <c r="S31" t="n">
-        <v>0.7124</v>
+        <v>0.7149</v>
       </c>
       <c r="T31" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="U31" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="V31" t="n">
         <v>0.906</v>
@@ -4448,56 +4463,588 @@
         <v>0.08333</v>
       </c>
       <c r="X31" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0.65511</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>6410-20-16-O</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/8-12 (male ORB) x 1 5/16-12 (female ORB port)</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>6410</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>1 5/8-12 (male ORB)</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>1 5/16-12 (female ORB port)</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 1.22 &gt;= port minor 1.22 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.906 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>OMi Side 1 ID 1.231 NOT applied (2026-09-25): wider than the female port it runs into (-16 port minor 1.22); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | DEEP BORE: through-bore 1.22 = port minor 1.2200 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.906 from the port face; the 120deg point would have ended 1.258 deep, -0.058 from the End A tip); female port reaches 0.294 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.098 at 0.469 from the tip (OK)</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>6410-20-16-O</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>6410-20-24-O</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.29904</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.7534999999999999</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="P32" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.7119</v>
+      </c>
+      <c r="T32" t="n">
+        <v>60</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0.93511</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.074</v>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>6410-20-24-O</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/8-12 (male ORB) x 1 7/8-12 (female ORB port)</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>6410</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>1 5/8-12 (male ORB)</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>1 7/8-12 (female ORB port)</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1874 Overall Length = 1.980 (table had 1.88) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>6410-20-24-O</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>6410-24-12-O</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1.22976</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="P33" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.7149</v>
+      </c>
+      <c r="T33" t="n">
+        <v>90</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0.53011</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>6410-24-12-O</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 7/8-12 (male ORB) x 1 1/16-12 (female ORB port)</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>6410</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>1 7/8-12 (male ORB)</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>1 1/16-12 (female ORB port)</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.97 &gt;= port minor 0.97 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.906 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>OMi Side 1 ID 0.981 NOT applied (2026-09-25): wider than the female port it runs into (-12 port minor 0.97); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.26 (Lengths to check!E11; website file said 1.000, a filler) = the Air-Way L33 1.26 already in this row -&gt; no change; OMi and Air-Way agree on the length | DEEP BORE: through-bore 0.97 = port minor 0.9700 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.906 from the port face; the 120deg point would have ended 1.186 deep, 0.074 from the End A tip); female port reaches 0.354 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.348 at 0.469 from the tip (OK)</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>6410-24-12-O</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>6410-24-16-O</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1.22976</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P34" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.7149</v>
+      </c>
+      <c r="T34" t="n">
+        <v>90</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0.65511</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>6410-24-16-O</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 7/8-12 (male ORB) x 1 5/16-12 (female ORB port)</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>6410</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>1 7/8-12 (male ORB)</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>1 5/16-12 (female ORB port)</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 1.22 &gt;= port minor 1.22 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.906 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>OMi Side 1 ID 1.231 NOT applied (2026-09-25): wider than the female port it runs into (-16 port minor 1.22); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.27 (Lengths to check!E12; website file said 1.000, a filler) = the Air-Way L33 1.27 already in this row -&gt; no change; OMi and Air-Way agree on the length | DEEP BORE: through-bore 1.22 = port minor 1.2200 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.906 from the port face; the 120deg point would have ended 1.258 deep, 0.012 from the End A tip); female port reaches 0.364 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.223 at 0.469 from the tip (OK)</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>6410-24-16-O</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>6410-24-20-O</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1.22976</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.8575</v>
+      </c>
+      <c r="P35" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.8205</v>
+      </c>
+      <c r="R35" t="n">
         <v>0.765</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="S35" t="n">
+        <v>0.7124</v>
+      </c>
+      <c r="T35" t="n">
+        <v>60</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="Y35" t="n">
         <v>0.81011</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="Z35" t="n">
         <v>1.75</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AA35" t="n">
         <v>1.31</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AB35" t="n">
         <v>0.844</v>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>6410-24-20-O</t>
         </is>
       </c>
-      <c r="AD31" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>ORB Reducer/Expander (male ORB x female ORB port), 1 7/8-12 (male ORB) x 1 5/8-12 (female ORB port)</t>
         </is>
       </c>
-      <c r="AE31" t="inlineStr">
+      <c r="AE35" t="inlineStr">
         <is>
           <t>6410</t>
         </is>
       </c>
-      <c r="AF31" t="inlineStr">
+      <c r="AF35" t="inlineStr">
         <is>
           <t>1 7/8-12 (male ORB)</t>
         </is>
       </c>
-      <c r="AG31" t="inlineStr">
+      <c r="AG35" t="inlineStr">
         <is>
           <t>1 5/8-12 (female ORB port)</t>
         </is>
       </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>ASSUMED</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
         <is>
           <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
         </is>
       </c>
-      <c r="AK31" t="inlineStr">
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L33@DRIVE=1.75~1.750; C1HEX@HEX=2.13~2.125; D@BORE=1.31~1.312</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
         <is>
           <t>6410-24-20-O</t>
         </is>

--- a/04_DESIGN_TABLES/DesignTable_6410_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6410_SW2.xlsx
@@ -601,32 +601,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6410-12-08-O</t>
+          <t>6410-24-20-O</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7216900000000001</v>
+        <v>1.22976</v>
       </c>
       <c r="D2" t="n">
-        <v>1.25</v>
+        <v>2.13</v>
       </c>
       <c r="E2" t="n">
-        <v>0.53125</v>
+        <v>0.9375</v>
       </c>
       <c r="F2" t="n">
         <v>0.469</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4725</v>
+        <v>0.878</v>
       </c>
       <c r="H2" t="n">
         <v>0.125</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0625</v>
+        <v>1.875</v>
       </c>
       <c r="J2" t="n">
         <v>0.08333</v>
@@ -644,55 +644,55 @@
         <v>0.08333</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4065</v>
+        <v>0.8575</v>
       </c>
       <c r="P2" t="n">
         <v>15</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.378</v>
+        <v>0.8205</v>
       </c>
       <c r="R2" t="n">
-        <v>0.34</v>
+        <v>0.765</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5436</v>
+        <v>0.7124</v>
       </c>
       <c r="T2" t="n">
         <v>60</v>
       </c>
       <c r="U2" t="n">
-        <v>0.68</v>
+        <v>1.53</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.906</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0625</v>
+        <v>0.08333</v>
       </c>
       <c r="X2" t="n">
-        <v>0.34</v>
+        <v>0.765</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.37383</v>
+        <v>0.81011</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.609</v>
+        <v>1.31</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.792</v>
+        <v>0.844</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>6410-12-08-O</t>
+          <t>6410-24-20-O</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 1/16-12 (male ORB) x 3/4-16 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 7/8-12 (male ORB) x 1 5/8-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -702,32 +702,32 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>1 1/16-12 (male ORB)</t>
+          <t>1 7/8-12 (male ORB)</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>3/4-16 (female ORB port)</t>
+          <t>1 5/8-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1856 Overall Length = 1.480 (table had 1.09); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1856 Side 1 ID = 0.609 (table had 0.68) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>Brennan 6410-12-08-O STEP overall 1.480 vs Air-Way 1.48: close (difference 0.000, normal between manufacturers)</t>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L33@DRIVE=1.75~1.750; C1HEX@HEX=2.13~2.125; D@BORE=1.31~1.312</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>6410-12-08-O</t>
+          <t>6410-24-20-O</t>
         </is>
       </c>
     </row>
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="C4" t="n">
-        <v>0.36084</v>
+        <v>0.39837</v>
       </c>
       <c r="D4" t="n">
-        <v>0.625</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E4" t="n">
         <v>0.21875</v>
@@ -943,13 +943,13 @@
         <v>0.21706</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AA4" t="n">
         <v>0.17</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.553</v>
+        <v>0.703</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -983,7 +983,12 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1838 Overall Length = 1.100 (table had 1.25); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1838 Hex Flat = 0.625 (table had 0.69) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1838 Overall Length = 1.100 (table had 1.25); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1838 Hex Flat = 0.625 (table had 0.69) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.25 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.1) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C1HEX@HEX: Air-Way 0.69 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.625) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.1 -&gt; Air-Way 1.25 | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 0.625 -&gt; Air-Way 0.69</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -999,13 +1004,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="C5" t="n">
-        <v>0.46881</v>
+        <v>0.50807</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="E5" t="n">
         <v>0.21875</v>
@@ -1071,13 +1076,13 @@
         <v>0.28007</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AA5" t="n">
         <v>0.17</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.551</v>
+        <v>0.591</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -1111,7 +1116,12 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1839 Overall Length = 1.160 (table had 1.2); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1839 Hex Flat = 0.812 (table had 0.88) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1839 Overall Length = 1.160 (table had 1.2); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1839 Hex Flat = 0.812 (table had 0.88) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.2 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.16) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C1HEX@HEX: Air-Way 0.88 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.812) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.16 -&gt; Air-Way 1.2 | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 0.812 -&gt; Air-Way 0.88</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1127,7 +1137,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="C6" t="n">
         <v>0.39837</v>
@@ -1199,13 +1209,13 @@
         <v>0.21706</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AA6" t="n">
         <v>0.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.573</v>
+        <v>0.483</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -1239,7 +1249,12 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1841 Overall Length = 1.120 (table had 1.03) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1841 Overall Length = 1.120 (table had 1.03) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.03 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.12) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.12 -&gt; Air-Way 1.03</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1255,7 +1270,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="C7" t="n">
         <v>0.50807</v>
@@ -1327,13 +1342,13 @@
         <v>0.28007</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AA7" t="n">
         <v>0.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.681</v>
+        <v>0.551</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
@@ -1367,7 +1382,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1842 Overall Length = 1.290 (table had 1.16) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1842 Overall Length = 1.290 (table had 1.16) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.16 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.29) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.29 -&gt; Air-Way 1.16</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -1383,7 +1403,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="C8" t="n">
         <v>0.57735</v>
@@ -1455,13 +1475,13 @@
         <v>0.37383</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AA8" t="n">
         <v>0.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.762</v>
+        <v>0.632</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -1495,12 +1515,12 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: Air-Way 1.32 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.45) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1843 = 1.450 (table had 1.32) | Brennan TFA TFA-p016-t03: agrees on L33@DRIVE, C1HEX@HEX, D@BORE</t>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1843 = 1.450 (table had 1.32) | Brennan TFA TFA-p016-t03: agrees on L33@DRIVE, C1HEX@HEX, D@BORE | 2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.45 -&gt; Air-Way 1.32</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -1516,7 +1536,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="C9" t="n">
         <v>0.50807</v>
@@ -1588,13 +1608,13 @@
         <v>0.21706</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="AA9" t="n">
         <v>0.38</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.553</v>
+        <v>0.253</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -1628,12 +1648,12 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.38 &gt;= port minor 0.38 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.547 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: Air-Way 0.8 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.1) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.38 &gt;= port minor 0.38 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.547 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1844 = 1.100 (table had 0.8) | Brennan TFA TFA-p016-t03: agrees on L33@DRIVE, C1HEX@HEX; DIFFERS on D@BORE 0.38 vs Brennan B DRILL 0.391 (built to the dimension source, s6) | DEEP BORE: through-bore 0.38 = port minor 0.3800 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.547 from the port face; the 120deg point would have ended 0.657 deep, 0.443 from the End A tip)</t>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1844 = 1.100 (table had 0.8) | Brennan TFA TFA-p016-t03: agrees on L33@DRIVE, C1HEX@HEX; DIFFERS on D@BORE 0.38 vs Brennan B DRILL 0.391 (built to the dimension source, s6) | 2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.1 -&gt; Air-Way 0.8 | DEEP BORE: through-bore 0.38 = port minor 0.3800 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.547 from the port face; the 120deg point would have ended 0.657 deep, 0.143 from the End A tip); female port reaches 0.253 from the End A tip, inside the End A thread/groove zone (0.438); radial wall there min 0.113 at 0.345 from the tip (OK)</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -1782,7 +1802,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="C11" t="n">
         <v>0.57735</v>
@@ -1854,13 +1874,13 @@
         <v>0.37383</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AA11" t="n">
         <v>0.39</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.722</v>
+        <v>0.622</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -1894,7 +1914,12 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1846 Overall Length = 1.410 (table had 1.31) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1846 Overall Length = 1.410 (table had 1.31) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.31 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.41) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.41 -&gt; Air-Way 1.31</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -1910,7 +1935,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="C12" t="n">
         <v>0.65241</v>
@@ -1982,13 +2007,13 @@
         <v>0.43866</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AA12" t="n">
         <v>0.39</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.699</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -2022,7 +2047,12 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1847 Overall Length = 1.480 (table had 1.47) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1847 Overall Length = 1.480 (table had 1.47) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.47 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.48) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.48 -&gt; Air-Way 1.47</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -2437,7 +2467,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="C16" t="n">
         <v>0.57735</v>
@@ -2509,13 +2539,13 @@
         <v>0.37383</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AA16" t="n">
         <v>0.48</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.632</v>
+        <v>0.652</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
@@ -2549,7 +2579,12 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1851 Overall Length = 1.320 (table had 1.34) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1851 Overall Length = 1.320 (table had 1.34) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.34 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.32) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.32 -&gt; Air-Way 1.34</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -2565,7 +2600,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="C17" t="n">
         <v>0.79674</v>
@@ -2637,13 +2672,13 @@
         <v>0.53011</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="AA17" t="n">
         <v>0.48</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.884</v>
+        <v>0.784</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
@@ -2677,7 +2712,12 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1853 Overall Length = 1.790 (table had 1.69) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1853 Overall Length = 1.790 (table had 1.69) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.69 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.79) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.79 -&gt; Air-Way 1.69</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -2955,11 +2995,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6410-12-10-O</t>
+          <t>6410-12-08-O</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.48</v>
+        <v>1.09</v>
       </c>
       <c r="C20" t="n">
         <v>0.7216900000000001</v>
@@ -2998,55 +3038,55 @@
         <v>0.08333</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4725</v>
+        <v>0.4065</v>
       </c>
       <c r="P20" t="n">
         <v>15</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.4441</v>
+        <v>0.378</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6309</v>
+        <v>0.5436</v>
       </c>
       <c r="T20" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8</v>
+        <v>0.68</v>
       </c>
       <c r="V20" t="n">
-        <v>0.781</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="X20" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.43866</v>
+        <v>0.37383</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.48</v>
+        <v>1.09</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.699</v>
+        <v>0.402</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>6410-12-10-O</t>
+          <t>6410-12-08-O</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 1/16-12 (male ORB) x 7/8-14 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 1/16-12 (male ORB) x 3/4-16 (female ORB port)</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
@@ -3061,7 +3101,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>7/8-14 (female ORB port)</t>
+          <t>3/4-16 (female ORB port)</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
@@ -3071,29 +3111,34 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1857 Overall Length = 1.480 (table had 1.56) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1856 Overall Length = 1.480 (table had 1.09); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1856 Side 1 ID = 0.609 (table had 0.68) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.09 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.48) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D@BORE: Air-Way 0.68 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.609) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.68 &gt;= port minor 0.68 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.688 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.48 -&gt; Air-Way 1.09 | 2026-10-20 Air-Way first: D@BORE OMi/Brennan 0.609 -&gt; Air-Way 0.68 | DEEP BORE: through-bore 0.68 = port minor 0.6800 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.688 from the port face; the 120deg point would have ended 0.884 deep, 0.206 from the End A tip); female port reaches 0.402 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.099 at 0.469 from the tip (OK); DIVERGENT LENGTH: Brennan 6410-12-08-O STEP overall 1.480 vs Air-Way L33 1.09 (Brennan: male -12 ORB end 0.594 + hex 0.886 carrying the whole -08 port; Air-Way puts the port inside the male end) - built to Air-Way per the project rule; confirm with OMi</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>6410-12-10-O</t>
+          <t>6410-12-08-O</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6410-12-12-O</t>
+          <t>6410-12-10-O</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="C21" t="n">
-        <v>0.79674</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="E21" t="n">
         <v>0.53125</v>
@@ -3126,55 +3171,55 @@
         <v>0.08333</v>
       </c>
       <c r="O21" t="n">
-        <v>0.575</v>
+        <v>0.4725</v>
       </c>
       <c r="P21" t="n">
         <v>15</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.538</v>
+        <v>0.4441</v>
       </c>
       <c r="R21" t="n">
-        <v>0.485</v>
+        <v>0.4</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7149</v>
+        <v>0.6309</v>
       </c>
       <c r="T21" t="n">
         <v>60</v>
       </c>
       <c r="U21" t="n">
-        <v>0.97</v>
+        <v>0.8</v>
       </c>
       <c r="V21" t="n">
-        <v>0.906</v>
+        <v>0.781</v>
       </c>
       <c r="W21" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="X21" t="n">
-        <v>0.485</v>
+        <v>0.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.53011</v>
+        <v>0.43866</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="AA21" t="n">
         <v>0.61</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.924</v>
+        <v>0.779</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>6410-12-12-O</t>
+          <t>6410-12-10-O</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 1/16-12 (male ORB) x 1 1/16-12 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 1/16-12 (male ORB) x 7/8-14 (female ORB port)</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
@@ -3189,7 +3234,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>1 1/16-12 (female ORB port)</t>
+          <t>7/8-14 (female ORB port)</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
@@ -3199,29 +3244,34 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1858 Overall Length = 1.830 (table had 1.75) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1857 Overall Length = 1.480 (table had 1.56) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.56 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.48) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.48 -&gt; Air-Way 1.56</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>6410-12-12-O</t>
+          <t>6410-12-10-O</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6410-12-16-O</t>
+          <t>6410-12-12-O</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="C22" t="n">
-        <v>0.94108</v>
+        <v>0.79674</v>
       </c>
       <c r="D22" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="E22" t="n">
         <v>0.53125</v>
@@ -3254,16 +3304,16 @@
         <v>0.08333</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7</v>
+        <v>0.575</v>
       </c>
       <c r="P22" t="n">
         <v>15</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.663</v>
+        <v>0.538</v>
       </c>
       <c r="R22" t="n">
-        <v>0.61</v>
+        <v>0.485</v>
       </c>
       <c r="S22" t="n">
         <v>0.7149</v>
@@ -3272,7 +3322,7 @@
         <v>60</v>
       </c>
       <c r="U22" t="n">
-        <v>1.22</v>
+        <v>0.97</v>
       </c>
       <c r="V22" t="n">
         <v>0.906</v>
@@ -3281,28 +3331,28 @@
         <v>0.08333</v>
       </c>
       <c r="X22" t="n">
-        <v>0.61</v>
+        <v>0.485</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.65511</v>
+        <v>0.53011</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AA22" t="n">
         <v>0.61</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.014</v>
+        <v>0.844</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>6410-12-16-O</t>
+          <t>6410-12-12-O</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 1/16-12 (male ORB) x 1 5/16-12 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 1/16-12 (male ORB) x 1 1/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
@@ -3317,7 +3367,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>1 5/16-12 (female ORB port)</t>
+          <t>1 1/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
@@ -3327,44 +3377,49 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1859 Overall Length = 1.920 (table had 1.88) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1858 Overall Length = 1.830 (table had 1.75) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.75 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.83) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.83 -&gt; Air-Way 1.75</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>6410-12-16-O</t>
+          <t>6410-12-12-O</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6410-16-04-O</t>
+          <t>6410-12-16-O</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>1.88</v>
       </c>
       <c r="C23" t="n">
-        <v>0.86603</v>
+        <v>0.94108</v>
       </c>
       <c r="D23" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="E23" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="F23" t="n">
         <v>0.469</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5975</v>
+        <v>0.4725</v>
       </c>
       <c r="H23" t="n">
         <v>0.125</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="J23" t="n">
         <v>0.08333</v>
@@ -3382,55 +3437,55 @@
         <v>0.08333</v>
       </c>
       <c r="O23" t="n">
-        <v>0.245</v>
+        <v>0.7</v>
       </c>
       <c r="P23" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.2233</v>
+        <v>0.663</v>
       </c>
       <c r="R23" t="n">
-        <v>0.19</v>
+        <v>0.61</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4116</v>
+        <v>0.7149</v>
       </c>
       <c r="T23" t="n">
         <v>60</v>
       </c>
       <c r="U23" t="n">
-        <v>0.38</v>
+        <v>1.22</v>
       </c>
       <c r="V23" t="n">
-        <v>0.547</v>
+        <v>0.906</v>
       </c>
       <c r="W23" t="n">
-        <v>0.05</v>
+        <v>0.08333</v>
       </c>
       <c r="X23" t="n">
-        <v>0.19</v>
+        <v>0.61</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.21706</v>
+        <v>0.65511</v>
       </c>
       <c r="Z23" t="n">
-        <v>1</v>
+        <v>1.88</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.368</v>
+        <v>0.61</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.453</v>
+        <v>0.974</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>6410-16-04-O</t>
+          <t>6410-12-16-O</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/16-12 (male ORB) x 7/16-20 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 1/16-12 (male ORB) x 1 5/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
@@ -3440,39 +3495,39 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>1 5/16-12 (male ORB)</t>
+          <t>1 1/16-12 (male ORB)</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>7/16-20 (female ORB port)</t>
+          <t>1 5/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): L33 = OMi real length (Lengths to check!E5); hex / Side 1 ID OMi website file Items row 1862; ORB end values from the end library (Q-TRANSFER-ENDLIB); user 2026-10-18: "this is verified information, use it"; one source -&gt; ASSUMED | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1859 Overall Length = 1.920 (table had 1.88) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.88 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.92) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): website length 1.000 was a filler; OMi gave 1.0 | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified) | female port reaches 0.343 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.380 at 0.469 from the tip (OK)</t>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.92 -&gt; Air-Way 1.88</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>6410-16-04-O</t>
+          <t>6410-12-16-O</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6410-16-06-O</t>
+          <t>6410-16-04-O</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -3515,55 +3570,55 @@
         <v>0.08333</v>
       </c>
       <c r="O24" t="n">
-        <v>0.309</v>
+        <v>0.245</v>
       </c>
       <c r="P24" t="n">
         <v>12</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.2865</v>
+        <v>0.2233</v>
       </c>
       <c r="R24" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4666</v>
+        <v>0.4116</v>
       </c>
       <c r="T24" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="V24" t="n">
-        <v>0.609</v>
+        <v>0.547</v>
       </c>
       <c r="W24" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="X24" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.28007</v>
+        <v>0.21706</v>
       </c>
       <c r="Z24" t="n">
         <v>1</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.5</v>
+        <v>0.368</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.391</v>
+        <v>0.453</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>6410-16-06-O</t>
+          <t>6410-16-04-O</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/16-12 (male ORB) x 9/16-18 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/16-12 (male ORB) x 7/16-20 (female ORB port)</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
@@ -3578,7 +3633,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>9/16-18 (female ORB port)</t>
+          <t>7/16-20 (female ORB port)</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
@@ -3588,28 +3643,28 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.5 &gt;= port minor 0.5 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.609 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): L33 = OMi real length (Lengths to check!E5); hex / Side 1 ID OMi website file Items row 1862; ORB end values from the end library (Q-TRANSFER-ENDLIB); user 2026-10-18: "this is verified information, use it"; one source -&gt; ASSUMED | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.0 (Lengths to check!E6; website file said 1.000, a filler) = the Air-Way L33 1 already in this row -&gt; no change; OMi and Air-Way agree on the length | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L33@DRIVE=1~1.000; C1HEX@HEX=1.5~1.500; D@BORE=0.5~0.508 | DEEP BORE: through-bore 0.5 = port minor 0.5000 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.609 from the port face; the 120deg point would have ended 0.753 deep, 0.247 from the End A tip); female port reaches 0.391 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.317 at 0.469 from the tip (OK)</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): website length 1.000 was a filler; OMi gave 1.0 | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified) | female port reaches 0.343 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.380 at 0.469 from the tip (OK)</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>6410-16-06-O</t>
+          <t>6410-16-04-O</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6410-16-08-O</t>
+          <t>6410-16-06-O</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
         <v>0.86603</v>
@@ -3648,55 +3703,55 @@
         <v>0.08333</v>
       </c>
       <c r="O25" t="n">
-        <v>0.4065</v>
+        <v>0.309</v>
       </c>
       <c r="P25" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.378</v>
+        <v>0.2865</v>
       </c>
       <c r="R25" t="n">
-        <v>0.34</v>
+        <v>0.25</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5436</v>
+        <v>0.4666</v>
       </c>
       <c r="T25" t="n">
         <v>90</v>
       </c>
       <c r="U25" t="n">
-        <v>0.68</v>
+        <v>0.5</v>
       </c>
       <c r="V25" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.609</v>
       </c>
       <c r="W25" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="X25" t="n">
-        <v>0.34</v>
+        <v>0.25</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.37383</v>
+        <v>0.28007</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.68</v>
+        <v>0.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.432</v>
+        <v>0.391</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>6410-16-08-O</t>
+          <t>6410-16-06-O</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/16-12 (male ORB) x 3/4-16 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/16-12 (male ORB) x 9/16-18 (female ORB port)</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
@@ -3711,38 +3766,38 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>3/4-16 (female ORB port)</t>
+          <t>9/16-18 (female ORB port)</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.68 &gt;= port minor 0.68 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.688 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.5 &gt;= port minor 0.5 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.609 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.12 (Lengths to check!E7; website file said 1.000, a filler) = the Air-Way L33 1.12 already in this row -&gt; no change; OMi and Air-Way agree on the length | DEEP BORE: through-bore 0.68 = port minor 0.6800 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.688 from the port face; the 120deg point would have ended 0.884 deep, 0.236 from the End A tip); female port reaches 0.432 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.224 at 0.469 from the tip (OK)</t>
+          <t>OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.0 (Lengths to check!E6; website file said 1.000, a filler) = the Air-Way L33 1 already in this row -&gt; no change; OMi and Air-Way agree on the length | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L33@DRIVE=1~1.000; C1HEX@HEX=1.5~1.500; D@BORE=0.5~0.508 | DEEP BORE: through-bore 0.5 = port minor 0.5000 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.609 from the port face; the 120deg point would have ended 0.753 deep, 0.247 from the End A tip); female port reaches 0.391 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.317 at 0.469 from the tip (OK)</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>6410-16-08-O</t>
+          <t>6410-16-06-O</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6410-16-10-O</t>
+          <t>6410-16-08-O</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.57</v>
+        <v>1.12</v>
       </c>
       <c r="C26" t="n">
         <v>0.86603</v>
@@ -3781,55 +3836,55 @@
         <v>0.08333</v>
       </c>
       <c r="O26" t="n">
-        <v>0.4725</v>
+        <v>0.4065</v>
       </c>
       <c r="P26" t="n">
         <v>15</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.4441</v>
+        <v>0.378</v>
       </c>
       <c r="R26" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="S26" t="n">
-        <v>0.6309</v>
+        <v>0.5436</v>
       </c>
       <c r="T26" t="n">
         <v>90</v>
       </c>
       <c r="U26" t="n">
-        <v>0.8</v>
+        <v>0.68</v>
       </c>
       <c r="V26" t="n">
-        <v>0.781</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="X26" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.43866</v>
+        <v>0.37383</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.57</v>
+        <v>1.12</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.8</v>
+        <v>0.68</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.789</v>
+        <v>0.432</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>6410-16-10-O</t>
+          <t>6410-16-08-O</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/16-12 (male ORB) x 7/8-14 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/16-12 (male ORB) x 3/4-16 (female ORB port)</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
@@ -3844,7 +3899,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>7/8-14 (female ORB port)</t>
+          <t>3/4-16 (female ORB port)</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
@@ -3854,28 +3909,28 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1865 Overall Length = 1.570 (table had 1.12) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.8 &gt;= port minor 0.8 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.781 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.68 &gt;= port minor 0.68 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.688 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>DEEP BORE: through-bore 0.8 = port minor 0.8000 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.781 from the port face; the 120deg point would have ended 1.012 deep, 0.558 from the End A tip)</t>
+          <t>OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.12 (Lengths to check!E7; website file said 1.000, a filler) = the Air-Way L33 1.12 already in this row -&gt; no change; OMi and Air-Way agree on the length | DEEP BORE: through-bore 0.68 = port minor 0.6800 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.688 from the port face; the 120deg point would have ended 0.884 deep, 0.236 from the End A tip); female port reaches 0.432 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.224 at 0.469 from the tip (OK)</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>6410-16-10-O</t>
+          <t>6410-16-08-O</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6410-16-12-O</t>
+          <t>6410-16-10-O</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.71</v>
+        <v>1.12</v>
       </c>
       <c r="C27" t="n">
         <v>0.86603</v>
@@ -3914,55 +3969,55 @@
         <v>0.08333</v>
       </c>
       <c r="O27" t="n">
-        <v>0.575</v>
+        <v>0.4725</v>
       </c>
       <c r="P27" t="n">
         <v>15</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.538</v>
+        <v>0.4441</v>
       </c>
       <c r="R27" t="n">
-        <v>0.485</v>
+        <v>0.4</v>
       </c>
       <c r="S27" t="n">
-        <v>0.7149</v>
+        <v>0.6309</v>
       </c>
       <c r="T27" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="U27" t="n">
-        <v>0.97</v>
+        <v>0.8</v>
       </c>
       <c r="V27" t="n">
-        <v>0.906</v>
+        <v>0.781</v>
       </c>
       <c r="W27" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="X27" t="n">
-        <v>0.485</v>
+        <v>0.4</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.53011</v>
+        <v>0.43866</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.71</v>
+        <v>1.12</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.804</v>
+        <v>0.339</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>6410-16-12-O</t>
+          <t>6410-16-10-O</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/16-12 (male ORB) x 1 1/16-12 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/16-12 (male ORB) x 7/8-14 (female ORB port)</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
@@ -3977,7 +4032,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>1 1/16-12 (female ORB port)</t>
+          <t>7/8-14 (female ORB port)</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
@@ -3987,29 +4042,34 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1866 Overall Length = 1.710 (table had 1.7) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1865 Overall Length = 1.570 (table had 1.12) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.12 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.57) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.8 &gt;= port minor 0.8 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.781 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.57 -&gt; Air-Way 1.12 | DEEP BORE: through-bore 0.8 = port minor 0.8000 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.781 from the port face; the 120deg point would have ended 1.012 deep, 0.108 from the End A tip); female port reaches 0.339 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.159 at 0.469 from the tip (OK)</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>6410-16-12-O</t>
+          <t>6410-16-10-O</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6410-16-16-O</t>
+          <t>6410-16-12-O</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="C28" t="n">
-        <v>0.94108</v>
+        <v>0.86603</v>
       </c>
       <c r="D28" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="E28" t="n">
         <v>0.65625</v>
@@ -4042,16 +4102,16 @@
         <v>0.08333</v>
       </c>
       <c r="O28" t="n">
-        <v>0.7</v>
+        <v>0.575</v>
       </c>
       <c r="P28" t="n">
         <v>15</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.663</v>
+        <v>0.538</v>
       </c>
       <c r="R28" t="n">
-        <v>0.61</v>
+        <v>0.485</v>
       </c>
       <c r="S28" t="n">
         <v>0.7149</v>
@@ -4060,7 +4120,7 @@
         <v>60</v>
       </c>
       <c r="U28" t="n">
-        <v>1.22</v>
+        <v>0.97</v>
       </c>
       <c r="V28" t="n">
         <v>0.906</v>
@@ -4069,28 +4129,28 @@
         <v>0.08333</v>
       </c>
       <c r="X28" t="n">
-        <v>0.61</v>
+        <v>0.485</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.65511</v>
+        <v>0.53011</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AA28" t="n">
         <v>0.84</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.904</v>
+        <v>0.794</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>6410-16-16-O</t>
+          <t>6410-16-12-O</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/16-12 (male ORB) x 1 5/16-12 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/16-12 (male ORB) x 1 1/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
@@ -4105,7 +4165,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>1 5/16-12 (female ORB port)</t>
+          <t>1 1/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
@@ -4115,34 +4175,34 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1868 Overall Length = 1.81 (table had 1.97) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1866 Overall Length = 1.710 (table had 1.7) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.7 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.71) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>B(2) printed "1 1/16-12" both passes (a -16 female end is 1 5/16-12; L33/C1/D3 progression supports -16) - as-printed, likely typo</t>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.71 -&gt; Air-Way 1.7</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>6410-16-16-O</t>
+          <t>6410-16-12-O</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6410-16-20-O</t>
+          <t>6410-16-16-O</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="C29" t="n">
-        <v>1.22687</v>
+        <v>0.94108</v>
       </c>
       <c r="D29" t="n">
-        <v>2.125</v>
+        <v>1.63</v>
       </c>
       <c r="E29" t="n">
         <v>0.65625</v>
@@ -4175,25 +4235,25 @@
         <v>0.08333</v>
       </c>
       <c r="O29" t="n">
-        <v>0.8575</v>
+        <v>0.7</v>
       </c>
       <c r="P29" t="n">
         <v>15</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.8205</v>
+        <v>0.663</v>
       </c>
       <c r="R29" t="n">
-        <v>0.765</v>
+        <v>0.61</v>
       </c>
       <c r="S29" t="n">
-        <v>0.7124</v>
+        <v>0.7149</v>
       </c>
       <c r="T29" t="n">
         <v>60</v>
       </c>
       <c r="U29" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="V29" t="n">
         <v>0.906</v>
@@ -4202,28 +4262,28 @@
         <v>0.08333</v>
       </c>
       <c r="X29" t="n">
-        <v>0.765</v>
+        <v>0.61</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.81011</v>
+        <v>0.65511</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="AA29" t="n">
         <v>0.84</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.234</v>
+        <v>1.064</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>6410-16-20-O</t>
+          <t>6410-16-16-O</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/16-12 (male ORB) x 1 5/8-12 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/16-12 (male ORB) x 1 5/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
@@ -4238,7 +4298,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>1 5/8-12 (female ORB port)</t>
+          <t>1 5/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
@@ -4248,44 +4308,49 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1869 Overall Length = 2.140 (table had 2); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1869 Hex Flat = 2.125 (table had 2) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1868 Overall Length = 1.81 (table had 1.97) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.97 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.81) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>B(2) printed "1 1/16-12" both passes (a -16 female end is 1 5/16-12; L33/C1/D3 progression supports -16) - as-printed, likely typo | 2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.81 -&gt; Air-Way 1.97</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>6410-16-20-O</t>
+          <t>6410-16-16-O</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6410-20-12-O</t>
+          <t>6410-16-20-O</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>1.08542</v>
+        <v>1.1547</v>
       </c>
       <c r="D30" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="F30" t="n">
         <v>0.469</v>
       </c>
       <c r="G30" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.5975</v>
       </c>
       <c r="H30" t="n">
         <v>0.125</v>
       </c>
       <c r="I30" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="J30" t="n">
         <v>0.08333</v>
@@ -4303,25 +4368,25 @@
         <v>0.08333</v>
       </c>
       <c r="O30" t="n">
-        <v>0.575</v>
+        <v>0.8575</v>
       </c>
       <c r="P30" t="n">
         <v>15</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.538</v>
+        <v>0.8205</v>
       </c>
       <c r="R30" t="n">
-        <v>0.485</v>
+        <v>0.765</v>
       </c>
       <c r="S30" t="n">
-        <v>0.7149</v>
+        <v>0.7124</v>
       </c>
       <c r="T30" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="U30" t="n">
-        <v>0.97</v>
+        <v>1.53</v>
       </c>
       <c r="V30" t="n">
         <v>0.906</v>
@@ -4330,28 +4395,28 @@
         <v>0.08333</v>
       </c>
       <c r="X30" t="n">
-        <v>0.485</v>
+        <v>0.765</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.53011</v>
+        <v>0.81011</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.97</v>
+        <v>0.84</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.294</v>
+        <v>1.094</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>6410-20-12-O</t>
+          <t>6410-16-20-O</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/8-12 (male ORB) x 1 1/16-12 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/16-12 (male ORB) x 1 5/8-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
@@ -4361,12 +4426,12 @@
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>1 5/8-12 (male ORB)</t>
+          <t>1 5/16-12 (male ORB)</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>1 1/16-12 (female ORB port)</t>
+          <t>1 5/8-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
@@ -4376,24 +4441,24 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.97 &gt;= port minor 0.97 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.906 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1869 Overall Length = 2.140 (table had 2); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1869 Hex Flat = 2.125 (table had 2) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 2 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.14) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C1HEX@HEX: Air-Way 2 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.125) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>OMi Side 1 ID 0.981 NOT applied (2026-09-25): wider than the female port it runs into (-12 port minor 0.97); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.2 (Lengths to check!E10; website file said 1.000, a filler) = the Air-Way L33 1.2 already in this row -&gt; no change; OMi and Air-Way agree on the length | DEEP BORE: through-bore 0.97 = port minor 0.9700 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.906 from the port face; the 120deg point would have ended 1.186 deep, 0.014 from the End A tip); female port reaches 0.294 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.223 at 0.469 from the tip (OK)</t>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 2.14 -&gt; Air-Way 2 | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 2.125 -&gt; Air-Way 2</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>6410-20-12-O</t>
+          <t>6410-16-20-O</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6410-20-16-O</t>
+          <t>6410-20-12-O</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -4436,16 +4501,16 @@
         <v>0.08333</v>
       </c>
       <c r="O31" t="n">
-        <v>0.7</v>
+        <v>0.575</v>
       </c>
       <c r="P31" t="n">
         <v>15</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.663</v>
+        <v>0.538</v>
       </c>
       <c r="R31" t="n">
-        <v>0.61</v>
+        <v>0.485</v>
       </c>
       <c r="S31" t="n">
         <v>0.7149</v>
@@ -4454,7 +4519,7 @@
         <v>90</v>
       </c>
       <c r="U31" t="n">
-        <v>1.22</v>
+        <v>0.97</v>
       </c>
       <c r="V31" t="n">
         <v>0.906</v>
@@ -4463,28 +4528,28 @@
         <v>0.08333</v>
       </c>
       <c r="X31" t="n">
-        <v>0.61</v>
+        <v>0.485</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.65511</v>
+        <v>0.53011</v>
       </c>
       <c r="Z31" t="n">
         <v>1.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.22</v>
+        <v>0.97</v>
       </c>
       <c r="AB31" t="n">
         <v>0.294</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>6410-20-16-O</t>
+          <t>6410-20-12-O</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/8-12 (male ORB) x 1 5/16-12 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/8-12 (male ORB) x 1 1/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
@@ -4499,7 +4564,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>1 5/16-12 (female ORB port)</t>
+          <t>1 1/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
@@ -4509,34 +4574,34 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 1.22 &gt;= port minor 1.22 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.906 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.97 &gt;= port minor 0.97 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.906 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>OMi Side 1 ID 1.231 NOT applied (2026-09-25): wider than the female port it runs into (-16 port minor 1.22); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | DEEP BORE: through-bore 1.22 = port minor 1.2200 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.906 from the port face; the 120deg point would have ended 1.258 deep, -0.058 from the End A tip); female port reaches 0.294 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.098 at 0.469 from the tip (OK)</t>
+          <t>OMi Side 1 ID 0.981 NOT applied (2026-09-25): wider than the female port it runs into (-12 port minor 0.97); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.2 (Lengths to check!E10; website file said 1.000, a filler) = the Air-Way L33 1.2 already in this row -&gt; no change; OMi and Air-Way agree on the length | DEEP BORE: through-bore 0.97 = port minor 0.9700 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.906 from the port face; the 120deg point would have ended 1.186 deep, 0.014 from the End A tip); female port reaches 0.294 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.223 at 0.469 from the tip (OK)</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>6410-20-16-O</t>
+          <t>6410-20-12-O</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6410-20-24-O</t>
+          <t>6410-20-16-O</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.98</v>
+        <v>1.2</v>
       </c>
       <c r="C32" t="n">
-        <v>1.29904</v>
+        <v>1.08542</v>
       </c>
       <c r="D32" t="n">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="E32" t="n">
         <v>0.8125</v>
@@ -4569,25 +4634,25 @@
         <v>0.08333</v>
       </c>
       <c r="O32" t="n">
-        <v>0.983</v>
+        <v>0.7</v>
       </c>
       <c r="P32" t="n">
         <v>15</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.946</v>
+        <v>0.663</v>
       </c>
       <c r="R32" t="n">
-        <v>0.89</v>
+        <v>0.61</v>
       </c>
       <c r="S32" t="n">
-        <v>0.7119</v>
+        <v>0.7149</v>
       </c>
       <c r="T32" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="U32" t="n">
-        <v>1.78</v>
+        <v>1.22</v>
       </c>
       <c r="V32" t="n">
         <v>0.906</v>
@@ -4596,28 +4661,28 @@
         <v>0.08333</v>
       </c>
       <c r="X32" t="n">
-        <v>0.89</v>
+        <v>0.61</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.93511</v>
+        <v>0.65511</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.98</v>
+        <v>1.2</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.074</v>
+        <v>0.294</v>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>6410-20-24-O</t>
+          <t>6410-20-16-O</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/8-12 (male ORB) x 1 7/8-12 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/8-12 (male ORB) x 1 5/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
@@ -4632,7 +4697,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>1 7/8-12 (female ORB port)</t>
+          <t>1 5/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
@@ -4642,44 +4707,49 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1874 Overall Length = 1.980 (table had 1.88) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 1.22 &gt;= port minor 1.22 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.906 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>OMi Side 1 ID 1.231 NOT applied (2026-09-25): wider than the female port it runs into (-16 port minor 1.22); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | DEEP BORE: through-bore 1.22 = port minor 1.2200 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.906 from the port face; the 120deg point would have ended 1.258 deep, -0.058 from the End A tip); female port reaches 0.294 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.098 at 0.469 from the tip (OK)</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>6410-20-24-O</t>
+          <t>6410-20-16-O</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6410-24-12-O</t>
+          <t>6410-20-24-O</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.26</v>
+        <v>1.88</v>
       </c>
       <c r="C33" t="n">
-        <v>1.22976</v>
+        <v>1.29904</v>
       </c>
       <c r="D33" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="F33" t="n">
         <v>0.469</v>
       </c>
       <c r="G33" t="n">
-        <v>0.878</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="H33" t="n">
         <v>0.125</v>
       </c>
       <c r="I33" t="n">
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
       <c r="J33" t="n">
         <v>0.08333</v>
@@ -4697,25 +4767,25 @@
         <v>0.08333</v>
       </c>
       <c r="O33" t="n">
-        <v>0.575</v>
+        <v>0.983</v>
       </c>
       <c r="P33" t="n">
         <v>15</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.538</v>
+        <v>0.946</v>
       </c>
       <c r="R33" t="n">
-        <v>0.485</v>
+        <v>0.89</v>
       </c>
       <c r="S33" t="n">
-        <v>0.7149</v>
+        <v>0.7119</v>
       </c>
       <c r="T33" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="U33" t="n">
-        <v>0.97</v>
+        <v>1.78</v>
       </c>
       <c r="V33" t="n">
         <v>0.906</v>
@@ -4724,28 +4794,28 @@
         <v>0.08333</v>
       </c>
       <c r="X33" t="n">
-        <v>0.485</v>
+        <v>0.89</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.53011</v>
+        <v>0.93511</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.26</v>
+        <v>1.88</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.97</v>
+        <v>1.08</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.354</v>
+        <v>0.974</v>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>6410-24-12-O</t>
+          <t>6410-20-24-O</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 7/8-12 (male ORB) x 1 1/16-12 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/8-12 (male ORB) x 1 7/8-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
@@ -4755,12 +4825,12 @@
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>1 7/8-12 (male ORB)</t>
+          <t>1 5/8-12 (male ORB)</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>1 1/16-12 (female ORB port)</t>
+          <t>1 7/8-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
@@ -4770,28 +4840,28 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.97 &gt;= port minor 0.97 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.906 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1874 Overall Length = 1.980 (table had 1.88) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.88 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.98) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>OMi Side 1 ID 0.981 NOT applied (2026-09-25): wider than the female port it runs into (-12 port minor 0.97); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.26 (Lengths to check!E11; website file said 1.000, a filler) = the Air-Way L33 1.26 already in this row -&gt; no change; OMi and Air-Way agree on the length | DEEP BORE: through-bore 0.97 = port minor 0.9700 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.906 from the port face; the 120deg point would have ended 1.186 deep, 0.074 from the End A tip); female port reaches 0.354 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.348 at 0.469 from the tip (OK)</t>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.98 -&gt; Air-Way 1.88</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>6410-24-12-O</t>
+          <t>6410-20-24-O</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6410-24-16-O</t>
+          <t>6410-24-12-O</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="C34" t="n">
         <v>1.22976</v>
@@ -4830,16 +4900,16 @@
         <v>0.08333</v>
       </c>
       <c r="O34" t="n">
-        <v>0.7</v>
+        <v>0.575</v>
       </c>
       <c r="P34" t="n">
         <v>15</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.663</v>
+        <v>0.538</v>
       </c>
       <c r="R34" t="n">
-        <v>0.61</v>
+        <v>0.485</v>
       </c>
       <c r="S34" t="n">
         <v>0.7149</v>
@@ -4848,7 +4918,7 @@
         <v>90</v>
       </c>
       <c r="U34" t="n">
-        <v>1.22</v>
+        <v>0.97</v>
       </c>
       <c r="V34" t="n">
         <v>0.906</v>
@@ -4857,28 +4927,28 @@
         <v>0.08333</v>
       </c>
       <c r="X34" t="n">
-        <v>0.61</v>
+        <v>0.485</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.65511</v>
+        <v>0.53011</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.22</v>
+        <v>0.97</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.364</v>
+        <v>0.354</v>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>6410-24-16-O</t>
+          <t>6410-24-12-O</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 7/8-12 (male ORB) x 1 5/16-12 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 7/8-12 (male ORB) x 1 1/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
@@ -4893,7 +4963,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>1 5/16-12 (female ORB port)</t>
+          <t>1 1/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
@@ -4903,28 +4973,28 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 1.22 &gt;= port minor 1.22 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.906 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.97 &gt;= port minor 0.97 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.906 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>OMi Side 1 ID 1.231 NOT applied (2026-09-25): wider than the female port it runs into (-16 port minor 1.22); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.27 (Lengths to check!E12; website file said 1.000, a filler) = the Air-Way L33 1.27 already in this row -&gt; no change; OMi and Air-Way agree on the length | DEEP BORE: through-bore 1.22 = port minor 1.2200 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.906 from the port face; the 120deg point would have ended 1.258 deep, 0.012 from the End A tip); female port reaches 0.364 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.223 at 0.469 from the tip (OK)</t>
+          <t>OMi Side 1 ID 0.981 NOT applied (2026-09-25): wider than the female port it runs into (-12 port minor 0.97); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.26 (Lengths to check!E11; website file said 1.000, a filler) = the Air-Way L33 1.26 already in this row -&gt; no change; OMi and Air-Way agree on the length | DEEP BORE: through-bore 0.97 = port minor 0.9700 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.906 from the port face; the 120deg point would have ended 1.186 deep, 0.074 from the End A tip); female port reaches 0.354 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.348 at 0.469 from the tip (OK)</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>6410-24-16-O</t>
+          <t>6410-24-12-O</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6410-24-20-O</t>
+          <t>6410-24-16-O</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="C35" t="n">
         <v>1.22976</v>
@@ -4963,25 +5033,25 @@
         <v>0.08333</v>
       </c>
       <c r="O35" t="n">
-        <v>0.8575</v>
+        <v>0.7</v>
       </c>
       <c r="P35" t="n">
         <v>15</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.8205</v>
+        <v>0.663</v>
       </c>
       <c r="R35" t="n">
-        <v>0.765</v>
+        <v>0.61</v>
       </c>
       <c r="S35" t="n">
-        <v>0.7124</v>
+        <v>0.7149</v>
       </c>
       <c r="T35" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="U35" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="V35" t="n">
         <v>0.906</v>
@@ -4990,28 +5060,28 @@
         <v>0.08333</v>
       </c>
       <c r="X35" t="n">
-        <v>0.765</v>
+        <v>0.61</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.81011</v>
+        <v>0.65511</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.844</v>
+        <v>0.364</v>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>6410-24-20-O</t>
+          <t>6410-24-16-O</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 7/8-12 (male ORB) x 1 5/8-12 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 7/8-12 (male ORB) x 1 5/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr">
@@ -5026,27 +5096,27 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>1 5/8-12 (female ORB port)</t>
+          <t>1 5/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 1.22 &gt;= port minor 1.22 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.906 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L33@DRIVE=1.75~1.750; C1HEX@HEX=2.13~2.125; D@BORE=1.31~1.312</t>
+          <t>OMi Side 1 ID 1.231 NOT applied (2026-09-25): wider than the female port it runs into (-16 port minor 1.22); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.27 (Lengths to check!E12; website file said 1.000, a filler) = the Air-Way L33 1.27 already in this row -&gt; no change; OMi and Air-Way agree on the length | DEEP BORE: through-bore 1.22 = port minor 1.2200 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.906 from the port face; the 120deg point would have ended 1.258 deep, 0.012 from the End A tip); female port reaches 0.364 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.223 at 0.469 from the tip (OK)</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>6410-24-20-O</t>
+          <t>6410-24-16-O</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_6410_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6410_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK35"/>
+  <dimension ref="A1:AK41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4458,17 +4458,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6410-20-12-O</t>
+          <t>6410-20-06-O</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1.2</v>
       </c>
       <c r="C31" t="n">
-        <v>1.08542</v>
+        <v>1.08253</v>
       </c>
       <c r="D31" t="n">
-        <v>1.88</v>
+        <v>1.875</v>
       </c>
       <c r="E31" t="n">
         <v>0.8125</v>
@@ -4501,55 +4501,55 @@
         <v>0.08333</v>
       </c>
       <c r="O31" t="n">
-        <v>0.575</v>
+        <v>0.309</v>
       </c>
       <c r="P31" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.538</v>
+        <v>0.2865</v>
       </c>
       <c r="R31" t="n">
-        <v>0.485</v>
+        <v>0.25</v>
       </c>
       <c r="S31" t="n">
-        <v>0.7149</v>
+        <v>0.4666</v>
       </c>
       <c r="T31" t="n">
         <v>90</v>
       </c>
       <c r="U31" t="n">
-        <v>0.97</v>
+        <v>0.5</v>
       </c>
       <c r="V31" t="n">
-        <v>0.906</v>
+        <v>0.609</v>
       </c>
       <c r="W31" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="X31" t="n">
-        <v>0.485</v>
+        <v>0.25</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.53011</v>
+        <v>0.28007</v>
       </c>
       <c r="Z31" t="n">
         <v>1.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.97</v>
+        <v>0.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.294</v>
+        <v>0.591</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>6410-20-12-O</t>
+          <t>6410-20-06-O</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/8-12 (male ORB) x 1 1/16-12 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/8-12 (male ORB) x 9/16-18 (female ORB port)</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>1 1/16-12 (female ORB port)</t>
+          <t>9/16-18 (female ORB port)</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
@@ -4574,34 +4574,34 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.97 &gt;= port minor 0.97 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.906 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): L33 = OMi real length (Lengths to check!E8); hex / Side 1 ID OMi website file Items row 1870; ORB end values from the end library (Q-TRANSFER-ENDLIB); user 2026-10-18: "this is verified information, use it"; one source -&gt; MISSING (held, below) -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): D@BORE capped at the port drill 0.5 (A11 Q-BOREWIDE; OMi Side 1 ID 0.509 reported to OMi); held reason removed -&gt; ASSUMED (OMi single source) | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.5 &gt;= port minor 0.5 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.609 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>OMi Side 1 ID 0.981 NOT applied (2026-09-25): wider than the female port it runs into (-12 port minor 0.97); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.2 (Lengths to check!E10; website file said 1.000, a filler) = the Air-Way L33 1.2 already in this row -&gt; no change; OMi and Air-Way agree on the length | DEEP BORE: through-bore 0.97 = port minor 0.9700 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.906 from the port face; the 120deg point would have ended 1.186 deep, 0.014 from the End A tip); female port reaches 0.294 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.223 at 0.469 from the tip (OK)</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): website length 1.000 was a filler; OMi gave 1.2; Side 1 ID 0.509 (Items!S1870) wider than the -06 port drill D3 0.5 -&gt; D@BORE left empty (Q-BOREWIDE, same as the 10 held rows) | 2026-10-20 batch-19 stage A_answered (not shipped): A11 cap D@BORE = D3 0.5 (OMi 0.509 wider than the port, report to OMi); MISSING -&gt; ASSUMED | DEEP BORE: through-bore 0.5 = port minor 0.5000 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.609 from the port face; the 120deg point would have ended 0.753 deep, 0.447 from the End A tip); female port reaches 0.591 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.473 at 0.591 from the tip (OK)</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>6410-20-12-O</t>
+          <t>6410-20-06-O</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6410-20-16-O</t>
+          <t>6410-20-08-O</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1.2</v>
       </c>
       <c r="C32" t="n">
-        <v>1.08542</v>
+        <v>1.08253</v>
       </c>
       <c r="D32" t="n">
-        <v>1.88</v>
+        <v>1.875</v>
       </c>
       <c r="E32" t="n">
         <v>0.8125</v>
@@ -4634,55 +4634,55 @@
         <v>0.08333</v>
       </c>
       <c r="O32" t="n">
-        <v>0.7</v>
+        <v>0.4065</v>
       </c>
       <c r="P32" t="n">
         <v>15</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.663</v>
+        <v>0.378</v>
       </c>
       <c r="R32" t="n">
-        <v>0.61</v>
+        <v>0.34</v>
       </c>
       <c r="S32" t="n">
-        <v>0.7149</v>
+        <v>0.5436</v>
       </c>
       <c r="T32" t="n">
         <v>90</v>
       </c>
       <c r="U32" t="n">
-        <v>1.22</v>
+        <v>0.68</v>
       </c>
       <c r="V32" t="n">
-        <v>0.906</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="W32" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="X32" t="n">
-        <v>0.61</v>
+        <v>0.34</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.65511</v>
+        <v>0.37383</v>
       </c>
       <c r="Z32" t="n">
         <v>1.2</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.22</v>
+        <v>0.68</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.294</v>
+        <v>0.512</v>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>6410-20-16-O</t>
+          <t>6410-20-08-O</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/8-12 (male ORB) x 1 5/16-12 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/8-12 (male ORB) x 3/4-16 (female ORB port)</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>1 5/16-12 (female ORB port)</t>
+          <t>3/4-16 (female ORB port)</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
@@ -4707,34 +4707,34 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 1.22 &gt;= port minor 1.22 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.906 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): L33 = OMi real length (Lengths to check!E9); hex / Side 1 ID OMi website file Items row 1871; ORB end values from the end library (Q-TRANSFER-ENDLIB); user 2026-10-18: "this is verified information, use it"; one source -&gt; MISSING (held, below) -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): D@BORE capped at the port drill 0.68 (A11 Q-BOREWIDE; OMi Side 1 ID 0.689 reported to OMi); held reason removed -&gt; ASSUMED (OMi single source) | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.68 &gt;= port minor 0.68 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.688 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>OMi Side 1 ID 1.231 NOT applied (2026-09-25): wider than the female port it runs into (-16 port minor 1.22); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | DEEP BORE: through-bore 1.22 = port minor 1.2200 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.906 from the port face; the 120deg point would have ended 1.258 deep, -0.058 from the End A tip); female port reaches 0.294 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.098 at 0.469 from the tip (OK)</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): website length 1.000 was a filler; OMi gave 1.2; Side 1 ID 0.689 (Items!S1871) wider than the -08 port drill D3 0.68 -&gt; D@BORE left empty (Q-BOREWIDE, same as the 10 held rows) | 2026-10-20 batch-19 stage A_answered (not shipped): A11 cap D@BORE = D3 0.68 (OMi 0.689 wider than the port, report to OMi); MISSING -&gt; ASSUMED | DEEP BORE: through-bore 0.68 = port minor 0.6800 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.688 from the port face; the 120deg point would have ended 0.884 deep, 0.316 from the End A tip); female port reaches 0.512 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.380 at 0.512 from the tip (OK)</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>6410-20-16-O</t>
+          <t>6410-20-08-O</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6410-20-24-O</t>
+          <t>6410-20-12-O</t>
         </is>
       </c>
       <c r="B33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1.08542</v>
+      </c>
+      <c r="D33" t="n">
         <v>1.88</v>
-      </c>
-      <c r="C33" t="n">
-        <v>1.29904</v>
-      </c>
-      <c r="D33" t="n">
-        <v>2.25</v>
       </c>
       <c r="E33" t="n">
         <v>0.8125</v>
@@ -4767,25 +4767,25 @@
         <v>0.08333</v>
       </c>
       <c r="O33" t="n">
-        <v>0.983</v>
+        <v>0.575</v>
       </c>
       <c r="P33" t="n">
         <v>15</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.946</v>
+        <v>0.538</v>
       </c>
       <c r="R33" t="n">
-        <v>0.89</v>
+        <v>0.485</v>
       </c>
       <c r="S33" t="n">
-        <v>0.7119</v>
+        <v>0.7149</v>
       </c>
       <c r="T33" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="U33" t="n">
-        <v>1.78</v>
+        <v>0.97</v>
       </c>
       <c r="V33" t="n">
         <v>0.906</v>
@@ -4794,28 +4794,28 @@
         <v>0.08333</v>
       </c>
       <c r="X33" t="n">
-        <v>0.89</v>
+        <v>0.485</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.93511</v>
+        <v>0.53011</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.88</v>
+        <v>1.2</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.08</v>
+        <v>0.97</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.974</v>
+        <v>0.294</v>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>6410-20-24-O</t>
+          <t>6410-20-12-O</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/8-12 (male ORB) x 1 7/8-12 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/8-12 (male ORB) x 1 1/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>1 7/8-12 (female ORB port)</t>
+          <t>1 1/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
@@ -4840,49 +4840,49 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1874 Overall Length = 1.980 (table had 1.88) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.88 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.98) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.97 &gt;= port minor 0.97 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.906 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.98 -&gt; Air-Way 1.88</t>
+          <t>OMi Side 1 ID 0.981 NOT applied (2026-09-25): wider than the female port it runs into (-12 port minor 0.97); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.2 (Lengths to check!E10; website file said 1.000, a filler) = the Air-Way L33 1.2 already in this row -&gt; no change; OMi and Air-Way agree on the length | DEEP BORE: through-bore 0.97 = port minor 0.9700 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.906 from the port face; the 120deg point would have ended 1.186 deep, 0.014 from the End A tip); female port reaches 0.294 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.223 at 0.469 from the tip (OK)</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>6410-20-24-O</t>
+          <t>6410-20-12-O</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6410-24-12-O</t>
+          <t>6410-20-16-O</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="C34" t="n">
-        <v>1.22976</v>
+        <v>1.08542</v>
       </c>
       <c r="D34" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="F34" t="n">
         <v>0.469</v>
       </c>
       <c r="G34" t="n">
-        <v>0.878</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="H34" t="n">
         <v>0.125</v>
       </c>
       <c r="I34" t="n">
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
       <c r="J34" t="n">
         <v>0.08333</v>
@@ -4900,16 +4900,16 @@
         <v>0.08333</v>
       </c>
       <c r="O34" t="n">
-        <v>0.575</v>
+        <v>0.7</v>
       </c>
       <c r="P34" t="n">
         <v>15</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.538</v>
+        <v>0.663</v>
       </c>
       <c r="R34" t="n">
-        <v>0.485</v>
+        <v>0.61</v>
       </c>
       <c r="S34" t="n">
         <v>0.7149</v>
@@ -4918,7 +4918,7 @@
         <v>90</v>
       </c>
       <c r="U34" t="n">
-        <v>0.97</v>
+        <v>1.22</v>
       </c>
       <c r="V34" t="n">
         <v>0.906</v>
@@ -4927,28 +4927,28 @@
         <v>0.08333</v>
       </c>
       <c r="X34" t="n">
-        <v>0.485</v>
+        <v>0.61</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.53011</v>
+        <v>0.65511</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.97</v>
+        <v>1.22</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.354</v>
+        <v>0.294</v>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>6410-24-12-O</t>
+          <t>6410-20-16-O</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 7/8-12 (male ORB) x 1 1/16-12 (female ORB port)</t>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/8-12 (male ORB) x 1 5/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
@@ -4958,12 +4958,12 @@
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>1 7/8-12 (male ORB)</t>
+          <t>1 5/8-12 (male ORB)</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>1 1/16-12 (female ORB port)</t>
+          <t>1 5/16-12 (female ORB port)</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
@@ -4973,49 +4973,49 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.97 &gt;= port minor 0.97 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.906 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 1.22 &gt;= port minor 1.22 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.906 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>OMi Side 1 ID 0.981 NOT applied (2026-09-25): wider than the female port it runs into (-12 port minor 0.97); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.26 (Lengths to check!E11; website file said 1.000, a filler) = the Air-Way L33 1.26 already in this row -&gt; no change; OMi and Air-Way agree on the length | DEEP BORE: through-bore 0.97 = port minor 0.9700 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.906 from the port face; the 120deg point would have ended 1.186 deep, 0.074 from the End A tip); female port reaches 0.354 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.348 at 0.469 from the tip (OK)</t>
+          <t>OMi Side 1 ID 1.231 NOT applied (2026-09-25): wider than the female port it runs into (-16 port minor 1.22); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | DEEP BORE: through-bore 1.22 = port minor 1.2200 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.906 from the port face; the 120deg point would have ended 1.258 deep, -0.058 from the End A tip); female port reaches 0.294 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.098 at 0.469 from the tip (OK)</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>6410-24-12-O</t>
+          <t>6410-20-16-O</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6410-24-16-O</t>
+          <t>6410-20-24-O</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.27</v>
+        <v>1.88</v>
       </c>
       <c r="C35" t="n">
-        <v>1.22976</v>
+        <v>1.29904</v>
       </c>
       <c r="D35" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="F35" t="n">
         <v>0.469</v>
       </c>
       <c r="G35" t="n">
-        <v>0.878</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="H35" t="n">
         <v>0.125</v>
       </c>
       <c r="I35" t="n">
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
       <c r="J35" t="n">
         <v>0.08333</v>
@@ -5033,25 +5033,25 @@
         <v>0.08333</v>
       </c>
       <c r="O35" t="n">
-        <v>0.7</v>
+        <v>0.983</v>
       </c>
       <c r="P35" t="n">
         <v>15</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.663</v>
+        <v>0.946</v>
       </c>
       <c r="R35" t="n">
-        <v>0.61</v>
+        <v>0.89</v>
       </c>
       <c r="S35" t="n">
-        <v>0.7149</v>
+        <v>0.7119</v>
       </c>
       <c r="T35" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="U35" t="n">
-        <v>1.22</v>
+        <v>1.78</v>
       </c>
       <c r="V35" t="n">
         <v>0.906</v>
@@ -5060,63 +5060,861 @@
         <v>0.08333</v>
       </c>
       <c r="X35" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0.93511</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>6410-20-24-O</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 5/8-12 (male ORB) x 1 7/8-12 (female ORB port)</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>6410</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>1 5/8-12 (male ORB)</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>1 7/8-12 (female ORB port)</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1874 Overall Length = 1.980 (table had 1.88) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.88 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.98) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.98 -&gt; Air-Way 1.88</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>6410-20-24-O</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>6410-24-12-O</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1.22976</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="P36" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.7149</v>
+      </c>
+      <c r="T36" t="n">
+        <v>90</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0.53011</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>6410-24-12-O</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 1 7/8-12 (male ORB) x 1 1/16-12 (female ORB port)</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>6410</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>1 7/8-12 (male ORB)</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>1 1/16-12 (female ORB port)</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.97 &gt;= port minor 0.97 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.906 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>OMi Side 1 ID 0.981 NOT applied (2026-09-25): wider than the female port it runs into (-12 port minor 0.97); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.26 (Lengths to check!E11; website file said 1.000, a filler) = the Air-Way L33 1.26 already in this row -&gt; no change; OMi and Air-Way agree on the length | DEEP BORE: through-bore 0.97 = port minor 0.9700 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.906 from the port face; the 120deg point would have ended 1.186 deep, 0.074 from the End A tip); female port reaches 0.354 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.348 at 0.469 from the tip (OK)</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>6410-24-12-O</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>6410-24-16-O</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1.22976</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P37" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="R37" t="n">
         <v>0.61</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="S37" t="n">
+        <v>0.7149</v>
+      </c>
+      <c r="T37" t="n">
+        <v>90</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="Y37" t="n">
         <v>0.65511</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="Z37" t="n">
         <v>1.27</v>
       </c>
-      <c r="AA35" t="n">
+      <c r="AA37" t="n">
         <v>1.22</v>
       </c>
-      <c r="AB35" t="n">
+      <c r="AB37" t="n">
         <v>0.364</v>
       </c>
-      <c r="AC35" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>6410-24-16-O</t>
         </is>
       </c>
-      <c r="AD35" t="inlineStr">
+      <c r="AD37" t="inlineStr">
         <is>
           <t>ORB Reducer/Expander (male ORB x female ORB port), 1 7/8-12 (male ORB) x 1 5/16-12 (female ORB port)</t>
         </is>
       </c>
-      <c r="AE35" t="inlineStr">
+      <c r="AE37" t="inlineStr">
         <is>
           <t>6410</t>
         </is>
       </c>
-      <c r="AF35" t="inlineStr">
+      <c r="AF37" t="inlineStr">
         <is>
           <t>1 7/8-12 (male ORB)</t>
         </is>
       </c>
-      <c r="AG35" t="inlineStr">
+      <c r="AG37" t="inlineStr">
         <is>
           <t>1 5/16-12 (female ORB port)</t>
         </is>
       </c>
-      <c r="AH35" t="inlineStr">
+      <c r="AH37" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="AI35" t="inlineStr">
+      <c r="AI37" t="inlineStr">
         <is>
           <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926 | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 1.22 &gt;= port minor 1.22 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.906 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
         </is>
       </c>
-      <c r="AJ35" t="inlineStr">
+      <c r="AJ37" t="inlineStr">
         <is>
           <t>OMi Side 1 ID 1.231 NOT applied (2026-09-25): wider than the female port it runs into (-16 port minor 1.22); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.27 (Lengths to check!E12; website file said 1.000, a filler) = the Air-Way L33 1.27 already in this row -&gt; no change; OMi and Air-Way agree on the length | DEEP BORE: through-bore 1.22 = port minor 1.2200 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.906 from the port face; the 120deg point would have ended 1.258 deep, 0.012 from the End A tip); female port reaches 0.364 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.223 at 0.469 from the tip (OK)</t>
         </is>
       </c>
-      <c r="AK35" t="inlineStr">
+      <c r="AK37" t="inlineStr">
         <is>
           <t>6410-24-16-O</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>6410-32-12-O</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1.58771</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.1905</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="P38" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.7149</v>
+      </c>
+      <c r="T38" t="n">
+        <v>90</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0.53011</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>6410-32-12-O</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 2 1/2-12 (male ORB) x 1 1/16-12 (female ORB port)</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>6410</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>2 1/2-12 (male ORB)</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>1 1/16-12 (female ORB port)</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): L33 = OMi real length (Lengths to check!E13); hex / Side 1 ID OMi website file Items row 1879; ORB end values from the end library (Q-TRANSFER-ENDLIB); user 2026-10-18: "this is verified information, use it"; one source -&gt; MISSING (held, below) -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): D@BORE capped at the port drill 0.97 (A11 Q-BOREWIDE; OMi Side 1 ID 0.981 reported to OMi); -32 male ORB groove width 0.125 = the Brennan 6400-32-32-O STEP value the generator library applies (A18; ORB_GRVW left empty on purpose); held reason removed -&gt; ASSUMED (OMi single source) | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.97 &gt;= port minor 0.97 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.906 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): website length 1.000 was a filler; OMi gave 1.43; Side 1 ID 0.981 (Items!S1879) wider than the -12 port drill D3 0.97 -&gt; D@BORE left empty (Q-BOREWIDE, same as the 10 held rows) | 2026-10-20 batch-19 stage A_answered (not shipped): A11 cap D@BORE = D3 0.97 (OMi 0.981 wider than the port, report to OMi); A18 groove 0.125 from the library; MISSING -&gt; ASSUMED | DEEP BORE: through-bore 0.97 = port minor 0.9700 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.906 from the port face; the 120deg point would have ended 1.186 deep, 0.244 from the End A tip); female port reaches 0.524 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.660 at 0.524 from the tip (OK)</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>6410-32-12-O</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>6410-32-16-O</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1.58771</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.1905</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P39" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.7149</v>
+      </c>
+      <c r="T39" t="n">
+        <v>90</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0.65511</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>6410-32-16-O</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 2 1/2-12 (male ORB) x 1 5/16-12 (female ORB port)</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>6410</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>2 1/2-12 (male ORB)</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>1 5/16-12 (female ORB port)</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): L33 = OMi real length (Lengths to check!E14); hex / Side 1 ID OMi website file Items row 1880; ORB end values from the end library (Q-TRANSFER-ENDLIB); user 2026-10-18: "this is verified information, use it"; one source -&gt; MISSING (held, below) -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): D@BORE capped at the port drill 1.22 (A11 Q-BOREWIDE; OMi Side 1 ID 1.231 reported to OMi); -32 male ORB groove width 0.125 = the Brennan 6400-32-32-O STEP value the generator library applies (A18; ORB_GRVW left empty on purpose); held reason removed -&gt; ASSUMED (OMi single source) | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 1.22 &gt;= port minor 1.22 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.906 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): website length 1.000 was a filler; OMi gave 1.43; Side 1 ID 1.231 (Items!S1880) wider than the -16 port drill D3 1.22 -&gt; D@BORE left empty (Q-BOREWIDE, same as the 10 held rows) | 2026-10-20 batch-19 stage A_answered (not shipped): A11 cap D@BORE = D3 1.22 (OMi 1.231 wider than the port, report to OMi); A18 groove 0.125 from the library; MISSING -&gt; ASSUMED | DEEP BORE: through-bore 1.22 = port minor 1.2200 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.906 from the port face; the 120deg point would have ended 1.258 deep, 0.172 from the End A tip); female port reaches 0.524 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.535 at 0.524 from the tip (OK)</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>6410-32-16-O</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>6410-32-20-O</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1.58771</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.1905</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.8575</v>
+      </c>
+      <c r="P40" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.8205</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.7124</v>
+      </c>
+      <c r="T40" t="n">
+        <v>90</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0.81011</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>6410-32-20-O</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 2 1/2-12 (male ORB) x 1 5/8-12 (female ORB port)</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>6410</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>2 1/2-12 (male ORB)</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>1 5/8-12 (female ORB port)</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1881 Side 1 ID = 1.544 (table had 1.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): unheld - A11 (D3 / D capped at the Air-Way per-size port drill, already applied), A18 (-32 male ORB groove width 0.125 = Brennan 6400-32-32-O STEP, applied by the generator library; ORB_GRVW left empty on purpose) -&gt; ASSUMED (Air-Way single source) | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 1.53 &gt;= port minor 1.53 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.906 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>ORB -32 groove width MEASURED 0.125 on the Brennan 6400-32-32-O STEP (2026-09-24, single source); Brennan STEP) | OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.43 (Lengths to check!E15; website file said 1.000, a filler) = the Air-Way L33 1.43 already in this row -&gt; no change; OMi and Air-Way agree on the length | D3@BORE 1.72 -&gt; 1.53: A11 Q-TRANSFER-D3: Air-Way per-size -20 port drill 1.53 instead of the impossible 1.72 (questions_20261008/merged.json orb-port-drill-per-size) | D@BORE 1.544 -&gt; 1.53: A11 Q-BOREWIDE: cap the through bore at the port drill 1.53 (report to OMi) | 2026-10-20 batch-19 stage A_answered (not shipped): MISSING -&gt; ASSUMED (A11 + A18 answered 2026-10-18; the -32 groove width comes from the end library) | DEEP BORE: through-bore 1.53 = port minor 1.5300 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.906 from the port face; the 120deg point would have ended 1.348 deep, 0.082 from the End A tip); female port reaches 0.524 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.380 at 0.524 from the tip (OK)</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>6410-32-20-O</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>6410-32-24-O</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1.58771</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1.1905</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="P41" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.7119</v>
+      </c>
+      <c r="T41" t="n">
+        <v>90</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0.93511</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>6410-32-24-O</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>ORB Reducer/Expander (male ORB x female ORB port), 2 1/2-12 (male ORB) x 1 7/8-12 (female ORB port)</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>6410</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>2 1/2-12 (male ORB)</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>1 7/8-12 (female ORB port)</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Air-Way s99 only (double-pass 45 rows; page footer claimed 48); male-ORB groove: measured/published set; female-ORB port per SAE J1926; L33@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1882 Overall Length = 1.440 (table had 1.43); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1882 Side 1 ID = 1.794 (table had 1.78) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L33@DRIVE: Air-Way 1.43 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.44) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): unheld - A11 (D3 / D capped at the Air-Way per-size port drill, already applied), A18 (-32 male ORB groove width 0.125 = Brennan 6400-32-32-O STEP, applied by the generator library; ORB_GRVW left empty on purpose) -&gt; ASSUMED (Air-Way single source) | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male ORB end: thread length + groove from the 6401/6405/6410 review tables; bore D from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 1.78 &gt;= port minor 1.78 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.906 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>ORB -32 groove width MEASURED 0.125 on the Brennan 6400-32-32-O STEP (2026-09-24, single source); Brennan STEP) | D@BORE 1.794 -&gt; 1.78: A11 Q-BOREWIDE: cap the through bore at the port drill 1.78 (report to OMi) | 2026-10-20 Air-Way first: L33@DRIVE OMi/Brennan 1.44 -&gt; Air-Way 1.43 | 2026-10-20 batch-19 stage A_answered (not shipped): MISSING -&gt; ASSUMED (A11 + A18 answered 2026-10-18; the -32 groove width comes from the end library) | DEEP BORE: through-bore 1.78 = port minor 1.7800 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.906 from the port face; the 120deg point would have ended 1.420 deep, 0.010 from the End A tip); female port reaches 0.524 from the End A tip, inside the End A thread/groove zone (0.594); radial wall there min 0.255 at 0.524 from the tip (OK)</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>6410-32-24-O</t>
         </is>
       </c>
     </row>
